--- a/docs/deliverables/out/Programme/Alignment/BIBS_Alignment_BRD-00_Integration_Inventory_v1.0.xlsx
+++ b/docs/deliverables/out/Programme/Alignment/BIBS_Alignment_BRD-00_Integration_Inventory_v1.0.xlsx
@@ -1482,12 +1482,12 @@
       </c>
       <c r="C12" s="12" t="inlineStr">
         <is>
-          <t>Mocks defined relative to T in the design</t>
+          <t>Trial migrations defined relative to T in the design</t>
         </is>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
-          <t>Mock 1 Apr-May 2027 (reference, clients, headers); Mock 2 Jun-Jul 2027 (all objects, L1-L5)</t>
+          <t>Trial migration 1 Apr-May 2027 (reference, clients, headers); Trial migration 2 Jun-Jul 2027 (all objects, L1-L5)</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
-          <t>UAT readiness statement by 30 Jul 2027; UAT plans and sign-off forms by 16 Jul 2027; UAT runs on migrated, masked data (Mock 3)</t>
+          <t>UAT readiness statement by 30 Jul 2027; UAT plans and sign-off forms by 16 Jul 2027; UAT runs on migrated, masked data (Trial migration 3)</t>
         </is>
       </c>
     </row>
@@ -1553,7 +1553,7 @@
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>Mock 3 = UAT load in Aug 2027; Mock 4 re-load in Oct 2027 after fixes</t>
+          <t>Trial migration 3 = UAT load in Aug 2027; Trial migration 4 re-load in Oct 2027 after fixes</t>
         </is>
       </c>
     </row>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
-          <t>What are the 12 x 5 hours? We need extended hours for batch and month-end test cycles, weekend migration mocks and the dress rehearsal; MSK and ElastiCache cannot be stopped.</t>
+          <t>What are the 12 x 5 hours? We need extended hours for batch and month-end test cycles, weekend migration trial migrations and the dress rehearsal; MSK and ElastiCache cannot be stopped.</t>
         </is>
       </c>
       <c r="E31" s="12" t="inlineStr">
@@ -2653,7 +2653,7 @@
       </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
-          <t>Which toolchain applies: GitLab (HW sheet), GitHub + Jenkins (infra diagram) or ArgoCD + Helm (diagram)? Container registry, image base (RHEL UBI or Alpine), SonarQube instance.</t>
+          <t>Which toolchain applies: GitLab (HW sheet), a second CI toolchain named in the IER (infra diagram) or ArgoCD + Helm (diagram)? Container registry, image base (RHEL UBI or Alpine), SonarQube instance.</t>
         </is>
       </c>
       <c r="E33" s="12" t="inlineStr">
@@ -7387,45 +7387,48 @@
     <cfRule type="cellIs" priority="8" operator="equal" dxfId="1" stopIfTrue="1">
       <formula>"CONFIGURE"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="9" operator="equal" dxfId="2" stopIfTrue="1">
+    <cfRule type="cellIs" priority="9" operator="equal" dxfId="1" stopIfTrue="1">
+      <formula>"RECOMMENDED"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="10" operator="equal" dxfId="2" stopIfTrue="1">
       <formula>"CHANGE"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="10" operator="equal" dxfId="2" stopIfTrue="1">
+    <cfRule type="cellIs" priority="11" operator="equal" dxfId="2" stopIfTrue="1">
       <formula>"PARTIAL"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="11" operator="equal" dxfId="2" stopIfTrue="1">
+    <cfRule type="cellIs" priority="12" operator="equal" dxfId="2" stopIfTrue="1">
       <formula>"IN PROGRESS"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="12" operator="equal" dxfId="2" stopIfTrue="1">
+    <cfRule type="cellIs" priority="13" operator="equal" dxfId="2" stopIfTrue="1">
       <formula>"OPEN"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="13" operator="equal" dxfId="3" stopIfTrue="1">
+    <cfRule type="cellIs" priority="14" operator="equal" dxfId="3" stopIfTrue="1">
       <formula>"NEW"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="14" operator="equal" dxfId="6" stopIfTrue="1">
+    <cfRule type="cellIs" priority="15" operator="equal" dxfId="6" stopIfTrue="1">
       <formula>"GAP"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="15" operator="equal" dxfId="6" stopIfTrue="1">
+    <cfRule type="cellIs" priority="16" operator="equal" dxfId="6" stopIfTrue="1">
       <formula>"FAIL"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="16" operator="equal" dxfId="6" stopIfTrue="1">
+    <cfRule type="cellIs" priority="17" operator="equal" dxfId="6" stopIfTrue="1">
       <formula>"FAILED"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="17" operator="equal" dxfId="6" stopIfTrue="1">
+    <cfRule type="cellIs" priority="18" operator="equal" dxfId="6" stopIfTrue="1">
       <formula>"BLOCKED"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="18" operator="equal" dxfId="4" stopIfTrue="1">
+    <cfRule type="cellIs" priority="19" operator="equal" dxfId="4" stopIfTrue="1">
       <formula>"OUT"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="19" operator="equal" dxfId="4" stopIfTrue="1">
+    <cfRule type="cellIs" priority="20" operator="equal" dxfId="4" stopIfTrue="1">
       <formula>"PARKED"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="20" operator="equal" dxfId="4" stopIfTrue="1">
+    <cfRule type="cellIs" priority="21" operator="equal" dxfId="4" stopIfTrue="1">
       <formula>"N/A"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A5:J531">
-    <cfRule type="expression" priority="21" dxfId="5">
+    <cfRule type="expression" priority="22" dxfId="5">
       <formula>AND(MOD(ROW(),2)=0,$A5&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7623,7 +7626,7 @@
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
-          <t>BIBS_FRS_BRD-13_*; BIBS_TestPlan_BRD-13_*; out/Migration/*</t>
+          <t>BIBS_FRS_BRD-13_*; BIBS_TestPlan_BRD-13_*; out/Drop-0_Setup_and_Data_Migration/Migration/*</t>
         </is>
       </c>
       <c r="D8" s="12" t="inlineStr">
@@ -8641,12 +8644,12 @@
       </c>
       <c r="B14" s="12" t="inlineStr">
         <is>
-          <t>HW sheet: GitLab Runner, AWS SSM, kubectl / helm on a bastion; infra diagram: GitHub + Jenkins; diagram: ArgoCD GitOps + Helm, Terraform + Crossplane</t>
+          <t>HW sheet: GitLab Runner, AWS SSM, kubectl / helm on a bastion; infra diagram: a second CI toolchain named in the IER; diagram: ArgoCD GitOps + Helm, Terraform + Crossplane</t>
         </is>
       </c>
       <c r="C14" s="12" t="inlineStr">
         <is>
-          <t>GitHub Actions (ci.yml: mvn verify, SonarQube, npm verify); plain Kubernetes manifests; no Helm chart</t>
+          <t>the CI pipeline (.gitlab-ci.yml: mvn verify, SonarQube, npm verify); plain Kubernetes manifests; no Helm chart</t>
         </is>
       </c>
       <c r="D14" s="30" t="inlineStr">
@@ -8919,45 +8922,48 @@
     <cfRule type="cellIs" priority="8" operator="equal" dxfId="1" stopIfTrue="1">
       <formula>"CONFIGURE"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="9" operator="equal" dxfId="2" stopIfTrue="1">
+    <cfRule type="cellIs" priority="9" operator="equal" dxfId="1" stopIfTrue="1">
+      <formula>"RECOMMENDED"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="10" operator="equal" dxfId="2" stopIfTrue="1">
       <formula>"CHANGE"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="10" operator="equal" dxfId="2" stopIfTrue="1">
+    <cfRule type="cellIs" priority="11" operator="equal" dxfId="2" stopIfTrue="1">
       <formula>"PARTIAL"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="11" operator="equal" dxfId="2" stopIfTrue="1">
+    <cfRule type="cellIs" priority="12" operator="equal" dxfId="2" stopIfTrue="1">
       <formula>"IN PROGRESS"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="12" operator="equal" dxfId="2" stopIfTrue="1">
+    <cfRule type="cellIs" priority="13" operator="equal" dxfId="2" stopIfTrue="1">
       <formula>"OPEN"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="13" operator="equal" dxfId="3" stopIfTrue="1">
+    <cfRule type="cellIs" priority="14" operator="equal" dxfId="3" stopIfTrue="1">
       <formula>"NEW"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="14" operator="equal" dxfId="6" stopIfTrue="1">
+    <cfRule type="cellIs" priority="15" operator="equal" dxfId="6" stopIfTrue="1">
       <formula>"GAP"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="15" operator="equal" dxfId="6" stopIfTrue="1">
+    <cfRule type="cellIs" priority="16" operator="equal" dxfId="6" stopIfTrue="1">
       <formula>"FAIL"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="16" operator="equal" dxfId="6" stopIfTrue="1">
+    <cfRule type="cellIs" priority="17" operator="equal" dxfId="6" stopIfTrue="1">
       <formula>"FAILED"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="17" operator="equal" dxfId="6" stopIfTrue="1">
+    <cfRule type="cellIs" priority="18" operator="equal" dxfId="6" stopIfTrue="1">
       <formula>"BLOCKED"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="18" operator="equal" dxfId="4" stopIfTrue="1">
+    <cfRule type="cellIs" priority="19" operator="equal" dxfId="4" stopIfTrue="1">
       <formula>"OUT"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="19" operator="equal" dxfId="4" stopIfTrue="1">
+    <cfRule type="cellIs" priority="20" operator="equal" dxfId="4" stopIfTrue="1">
       <formula>"PARKED"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="20" operator="equal" dxfId="4" stopIfTrue="1">
+    <cfRule type="cellIs" priority="21" operator="equal" dxfId="4" stopIfTrue="1">
       <formula>"N/A"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A5:F521">
-    <cfRule type="expression" priority="21" dxfId="5">
+    <cfRule type="expression" priority="22" dxfId="5">
       <formula>AND(MOD(ROW(),2)=0,$A5&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9398,7 +9404,7 @@
       </c>
       <c r="G5" s="12" t="inlineStr">
         <is>
-          <t>Demo data; jobs run on the single pod</t>
+          <t>Seed data; jobs run on the single pod</t>
         </is>
       </c>
     </row>
@@ -9546,7 +9552,7 @@
       </c>
       <c r="G9" s="12" t="inlineStr">
         <is>
-          <t>Migration mock loads run here (Mock 3)</t>
+          <t>Migration trial-migration loads run here (Trial migration 3)</t>
         </is>
       </c>
     </row>

--- a/docs/deliverables/out/Programme/Alignment/BIBS_Alignment_BRD-00_Integration_Inventory_v1.0.xlsx
+++ b/docs/deliverables/out/Programme/Alignment/BIBS_Alignment_BRD-00_Integration_Inventory_v1.0.xlsx
@@ -2591,7 +2591,7 @@
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
-          <t>What are the 12 x 5 hours? We need extended hours for batch and month-end test cycles, weekend migration trial migrations and the dress rehearsal; MSK and ElastiCache cannot be stopped.</t>
+          <t>What are the 12 x 5 hours? We need extended hours for batch and month-end test cycles, weekend trial migrations and the dress rehearsal; MSK and ElastiCache cannot be stopped.</t>
         </is>
       </c>
       <c r="E31" s="12" t="inlineStr">
@@ -9552,7 +9552,7 @@
       </c>
       <c r="G9" s="12" t="inlineStr">
         <is>
-          <t>Migration trial-migration loads run here (Trial migration 3)</t>
+          <t>Trial-migration loads run here (Trial migration 3)</t>
         </is>
       </c>
     </row>

--- a/docs/deliverables/out/Programme/Alignment/BIBS_Alignment_BRD-00_Integration_Inventory_v1.0.xlsx
+++ b/docs/deliverables/out/Programme/Alignment/BIBS_Alignment_BRD-00_Integration_Inventory_v1.0.xlsx
@@ -14,30 +14,30 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Drop map" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Documents by drop" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Infrastructure" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S3 changes" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S3 documents" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="K8s sizing" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Timeline" sheetId="10" state="visible" r:id="rId10"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Questions" sheetId="11" state="visible" r:id="rId11"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_lists" sheetId="12" state="hidden" r:id="rId12"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'README'!$A$4:$D$64</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'README'!$A$4:$D$55</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'README'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Integrations'!$A$4:$M$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Integrations'!$A$4:$I$24</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Integrations'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Other interfaces'!$A$4:$D$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Other interfaces'!$A$4:$C$11</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Other interfaces'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Drop map'!$A$4:$J$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Drop map'!$A$4:$H$31</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Drop map'!$4:$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Documents by drop'!$A$4:$F$27</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'Documents by drop'!$4:$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Infrastructure'!$A$4:$F$21</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="6">'Infrastructure'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'S3 changes'!$A$4:$C$18</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="7">'S3 changes'!$4:$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'S3 documents'!$A$4:$B$18</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="7">'S3 documents'!$4:$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'K8s sizing'!$A$4:$G$16</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="8">'K8s sizing'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Timeline'!$A$4:$D$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Timeline'!$A$4:$C$20</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="9">'Timeline'!$4:$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Questions'!$A$4:$G$39</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="10">'Questions'!$4:$4</definedName>
@@ -49,7 +49,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="21">
+  <fonts count="16">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -132,36 +132,6 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="002E7D32"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00004EA8"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="008A5A00"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="004527A0"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00656565"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
       <color rgb="00C62828"/>
       <sz val="10"/>
     </font>
@@ -172,7 +142,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -187,26 +157,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00E5F5FF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E8F5E9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF4D6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00EDE7F6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F6F6F6"/>
       </patternFill>
     </fill>
     <fill>
@@ -256,7 +206,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -286,22 +236,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -325,6 +260,14 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <dxfs count="7">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00E5F5FF"/>
+          <bgColor rgb="00E5F5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <b val="1"/>
@@ -376,32 +319,24 @@
     <dxf>
       <font>
         <b val="1"/>
+        <color rgb="00C62828"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FDECEA"/>
+          <bgColor rgb="00FDECEA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
         <color rgb="00656565"/>
       </font>
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="00F6F6F6"/>
           <bgColor rgb="00F6F6F6"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="00E5F5FF"/>
-          <bgColor rgb="00E5F5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color rgb="00C62828"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="00FDECEA"/>
-          <bgColor rgb="00FDECEA"/>
         </patternFill>
       </fill>
     </dxf>
@@ -509,7 +444,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>43</row>
+      <row>37</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="971550" cy="285750"/>
@@ -822,7 +757,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B4:E44"/>
+  <dimension ref="B4:E38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -856,7 +791,7 @@
     <row r="8">
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Drops, integrations and infrastructure: BDOI plan against BIBS as built</t>
+          <t>Drops, integrations and infrastructure: BDOI plan against BIBS</t>
         </is>
       </c>
     </row>
@@ -1054,12 +989,12 @@
     <row r="26">
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>S3 changes</t>
+          <t>S3 documents</t>
         </is>
       </c>
       <c r="C26" s="12" t="inlineStr">
         <is>
-          <t>Build item: documents and files in Amazon S3</t>
+          <t>Documents and files in Amazon S3</t>
         </is>
       </c>
       <c r="D26" s="12" t="n">
@@ -1121,110 +1056,38 @@
     <row r="32">
       <c r="B32" s="15" t="inlineStr">
         <is>
-          <t>FIT</t>
+          <t>GAP</t>
         </is>
       </c>
       <c r="C32" s="16" t="inlineStr">
         <is>
-          <t>Works today</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="B33" s="17" t="inlineStr">
-        <is>
-          <t>CONFIGURE</t>
-        </is>
-      </c>
-      <c r="C33" s="16" t="inlineStr">
-        <is>
-          <t>Set-up only (layout, parameters)</t>
+          <t>Missing in the IER or the plan</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="B34" s="18" t="inlineStr">
-        <is>
-          <t>CHANGE</t>
-        </is>
-      </c>
-      <c r="C34" s="16" t="inlineStr">
-        <is>
-          <t>Extends an existing seam or module</t>
+      <c r="B34" s="17" t="inlineStr">
+        <is>
+          <t>Integration meanings are those given by BDOI on 26-Sep-2026 (answer A2); 'Our understanding' is the project team's reading and is confirmed through the IQ questions.</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="B35" s="19" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="C35" s="16" t="inlineStr">
-        <is>
-          <t>New build</t>
+      <c r="B35" s="17" t="inlineStr">
+        <is>
+          <t>Documents and attachments live in Amazon S3 only (answer A4); the sheet 'S3 documents' lists the proposal.</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="B36" s="20" t="inlineStr">
-        <is>
-          <t>OUT</t>
-        </is>
-      </c>
-      <c r="C36" s="16" t="inlineStr">
-        <is>
-          <t>Out of scope</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="B37" s="15" t="inlineStr">
-        <is>
-          <t>BUILT</t>
-        </is>
-      </c>
-      <c r="C37" s="16" t="inlineStr">
-        <is>
-          <t>BRD built in BIBS</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="B38" s="21" t="inlineStr">
-        <is>
-          <t>GAP</t>
-        </is>
-      </c>
-      <c r="C38" s="16" t="inlineStr">
-        <is>
-          <t>Missing in the IER or the plan</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="B40" s="22" t="inlineStr">
-        <is>
-          <t>Integration meanings are those given by BDOI on 26-Sep-2026 (answer A2); 'Our understanding' is the project team's reading and is confirmed through the IQ questions.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="B41" s="22" t="inlineStr">
-        <is>
-          <t>Documents and attachments live in Amazon S3 only (answer A4); the sheet 'S3 changes' lists the build item.</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="B42" s="22" t="inlineStr">
-        <is>
-          <t>Sources: BDOI drop plan and timeline slides, IER workbook v20, concept paper (superseded), docs/architecture/PROGRAMME_ALIGNMENT.md.</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="26" customHeight="1">
-      <c r="B44" s="23" t="inlineStr">
+      <c r="B36" s="17" t="inlineStr">
+        <is>
+          <t>Sources: BDOI drop plan and timeline slides, IER workbook v20, concept paper (superseded).</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="26" customHeight="1">
+      <c r="B38" s="18" t="inlineStr">
         <is>
           <t>Prepared by iorta TechNXT for BDOI. Confidential – BDOI.</t>
         </is>
@@ -1264,52 +1127,45 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="44" customWidth="1" min="3" max="3"/>
-    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="80" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="24" t="inlineStr">
+      <c r="A1" s="19" t="inlineStr">
         <is>
           <t>Timeline</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="27" t="inlineStr">
+      <c r="A2" s="22" t="inlineStr">
         <is>
           <t>BDOI timeline against the BIBS plan</t>
         </is>
       </c>
     </row>
     <row r="3" ht="6" customHeight="1">
-      <c r="A3" s="28" t="n"/>
-      <c r="B3" s="28" t="n"/>
-      <c r="C3" s="28" t="n"/>
-      <c r="D3" s="28" t="n"/>
+      <c r="A3" s="23" t="n"/>
+      <c r="B3" s="23" t="n"/>
+      <c r="C3" s="23" t="n"/>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="29" t="inlineStr">
+      <c r="A4" s="24" t="inlineStr">
         <is>
           <t>Stream</t>
         </is>
       </c>
-      <c r="B4" s="29" t="inlineStr">
+      <c r="B4" s="24" t="inlineStr">
         <is>
           <t>BDOI window</t>
         </is>
       </c>
-      <c r="C4" s="29" t="inlineStr">
-        <is>
-          <t>Status today</t>
-        </is>
-      </c>
-      <c r="D4" s="29" t="inlineStr">
+      <c r="C4" s="24" t="inlineStr">
         <is>
           <t>What we deliver, by when</t>
         </is>
@@ -1328,12 +1184,7 @@
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>FRS v1.0 of BRD-00, 1, 2, 3, 5, 6, 9, 10, 11, 12, 13 issued 25-26 Sep 2026; register v1.1</t>
-        </is>
-      </c>
-      <c r="D5" s="12" t="inlineStr">
-        <is>
-          <t>FRS v1.1 with BDOI comments by 13 Nov 2026; sign-off by 30 Nov 2026; answers to the build-shaping IQ / DCR items by 16 Oct 2026</t>
+          <t>FRS v1.0 of BRD-00, 1, 2, 3, 5, 6, 9, 10, 11, 12, 13 and register v1.1 issued 25-26 Sep 2026; FRS v1.1 with BDOI comments by 13 Nov 2026; sign-off by 30 Nov 2026; answers to the priority-1 IQ / DCR items by 16 Oct 2026</t>
         </is>
       </c>
     </row>
@@ -1350,12 +1201,7 @@
       </c>
       <c r="C6" s="12" t="inlineStr">
         <is>
-          <t>Migration pack v1.0 issued 26 Sep 2026 (strategy, workbook, runbook, reconciliation)</t>
-        </is>
-      </c>
-      <c r="D6" s="12" t="inlineStr">
-        <is>
-          <t>Object decisions (G1) and layouts frozen by 30 Nov 2026; first full extracts by 15 Jan 2027</t>
+          <t>Migration pack v1.0 issued 26 Sep 2026 (strategy, workbook, runbook, reconciliation); object decisions (G1) and layouts frozen by 30 Nov 2026; first full extracts by 15 Jan 2027</t>
         </is>
       </c>
     </row>
@@ -1372,19 +1218,14 @@
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>FRS v1.0 of BRD-4, 7, 8 issued; EB FRS to re-issue without the portal</t>
-        </is>
-      </c>
-      <c r="D7" s="12" t="inlineStr">
-        <is>
-          <t>Sign-off by 26 Feb 2027; EGL, EDP, CARMS, insurer specifications from BDOI IT by 31 Jan 2027</t>
+          <t>FRS v1.0 of BRD-4, 7, 8 issued; EB FRS re-issued without the portal; sign-off by 26 Feb 2027; EGL, EDP, CARMS and insurer specifications from BDOI IT by 31 Jan 2027</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="12" t="inlineStr">
         <is>
-          <t>Build Drop 1 (waves 1 and 2)</t>
+          <t>Development Drop 1</t>
         </is>
       </c>
       <c r="B8" s="12" t="inlineStr">
@@ -1394,19 +1235,14 @@
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
-          <t>Built: BRD-1, 2, 3, 4, 5, 10, 11. To build: BRD-12 SP, BRD-6 RN, BRD-9 CSF (account maintenance), EIAM, UIDM-ISC, S3 store, bank channel layouts</t>
-        </is>
-      </c>
-      <c r="D8" s="12" t="inlineStr">
-        <is>
-          <t>Wave 1 (Nov-Dec): SP, RN foundation, EIAM, S3 store. Wave 2 (Jan-Feb): RN completion, bank channels, changes from signed FRS</t>
+          <t>Submitted Policies, Renewal, CSF account maintenance, EIAM, UIDM-ISC, the S3 document store, bank channel layouts and the changes from the signed FRS</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="12" t="inlineStr">
         <is>
-          <t>Build Migration</t>
+          <t>Development Migration</t>
         </is>
       </c>
       <c r="B9" s="12" t="inlineStr">
@@ -1416,19 +1252,14 @@
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>Designed (DM0-DM3)</t>
-        </is>
-      </c>
-      <c r="D9" s="12" t="inlineStr">
-        <is>
-          <t>Migration console and loaders by 31 Mar 2027</t>
+          <t>Migration Console and loaders by 31 Mar 2027</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="12" t="inlineStr">
         <is>
-          <t>Build Drop 2 (wave 3)</t>
+          <t>Development Drop 2</t>
         </is>
       </c>
       <c r="B10" s="12" t="inlineStr">
@@ -1438,12 +1269,7 @@
       </c>
       <c r="C10" s="12" t="inlineStr">
         <is>
-          <t>Claims being built; EB, CSF (rest) designed</t>
-        </is>
-      </c>
-      <c r="D10" s="12" t="inlineStr">
-        <is>
-          <t>Claims, EB without portal, CSF, EGL / EDP / insurer adapters, other reports by 30 Apr 2027</t>
+          <t>Claims, EB without portal, CSF, EGL / EDP / insurer interfaces and other reports by 30 Apr 2027</t>
         </is>
       </c>
     </row>
@@ -1460,12 +1286,7 @@
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>Test plans v1.0 for BRD-1 to BRD-13</t>
-        </is>
-      </c>
-      <c r="D11" s="12" t="inlineStr">
-        <is>
-          <t>Test plans approved by 18 Dec 2026; SIT environment with S3, MSK, ElastiCache by 4 Jan 2027</t>
+          <t>Test plans v1.0 for BRD-1 to BRD-13 issued; test plans approved by 18 Dec 2026; SIT environment with S3, MSK and ElastiCache by 4 Jan 2027</t>
         </is>
       </c>
     </row>
@@ -1482,11 +1303,6 @@
       </c>
       <c r="C12" s="12" t="inlineStr">
         <is>
-          <t>Trial migrations defined relative to T in the design</t>
-        </is>
-      </c>
-      <c r="D12" s="12" t="inlineStr">
-        <is>
           <t>Trial migration 1 Apr-May 2027 (reference, clients, headers); Trial migration 2 Jun-Jul 2027 (all objects, L1-L5)</t>
         </is>
       </c>
@@ -1504,11 +1320,6 @@
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D13" s="12" t="inlineStr">
-        <is>
           <t>Drop 2 test plans approved by 30 Jun 2027</t>
         </is>
       </c>
@@ -1526,11 +1337,6 @@
       </c>
       <c r="C14" s="12" t="inlineStr">
         <is>
-          <t>UAT readiness programme (deliverables README)</t>
-        </is>
-      </c>
-      <c r="D14" s="12" t="inlineStr">
-        <is>
           <t>UAT readiness statement by 30 Jul 2027; UAT plans and sign-off forms by 16 Jul 2027; UAT runs on migrated, masked data (Trial migration 3)</t>
         </is>
       </c>
@@ -1548,11 +1354,6 @@
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D15" s="12" t="inlineStr">
-        <is>
           <t>Trial migration 3 = UAT load in Aug 2027; Trial migration 4 re-load in Oct 2027 after fixes</t>
         </is>
       </c>
@@ -1570,11 +1371,6 @@
       </c>
       <c r="C16" s="12" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D16" s="12" t="inlineStr">
-        <is>
           <t>Readiness statement for Drop 2 by 30 Sep 2027</t>
         </is>
       </c>
@@ -1592,12 +1388,7 @@
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>Performance plan (item 28); peak 429 concurrent until DCR-166</t>
-        </is>
-      </c>
-      <c r="D17" s="12" t="inlineStr">
-        <is>
-          <t>Pre-Prod ready by 1 Oct 2027; an early security scan in SIT (Jun 2027) proposed so findings do not arrive in December</t>
+          <t>Performance plan (item 28), peak 429 concurrent until DCR-166; Pre-Prod ready by 1 Oct 2027; an early security scan in SIT (Jun 2027) proposed so findings do not arrive in December</t>
         </is>
       </c>
     </row>
@@ -1614,12 +1405,7 @@
       </c>
       <c r="C18" s="12" t="inlineStr">
         <is>
-          <t>Cutover runbook v1.0 (T-30 to T+30)</t>
-        </is>
-      </c>
-      <c r="D18" s="12" t="inlineStr">
-        <is>
-          <t>Dress rehearsal on Pre-Prod in Nov - Dec 2027; go / no-go on T-1</t>
+          <t>Cutover runbook v1.0 (T-30 to T+30); dress rehearsal on Pre-Prod in Nov - Dec 2027; go / no-go on T-1</t>
         </is>
       </c>
     </row>
@@ -1636,12 +1422,7 @@
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>Runbook, observability, alerts, error catalogue (items 24, 35, 38)</t>
-        </is>
-      </c>
-      <c r="D19" s="12" t="inlineStr">
-        <is>
-          <t>Evidence pack by 15 Dec 2027</t>
+          <t>Runbook, observability, alerts and error catalogue (items 24, 35, 38); evidence pack by 15 Dec 2027</t>
         </is>
       </c>
     </row>
@@ -1658,22 +1439,17 @@
       </c>
       <c r="C20" s="12" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D20" s="12" t="inlineStr">
-        <is>
           <t>T to be fixed (IQ01): proposed Mon 3 Jan 2028, legacy freeze after the EOD of Wed 29 Dec 2027</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:D20"/>
+  <autoFilter ref="A4:C20"/>
   <mergeCells count="1">
-    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A2:C2"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:D520">
-    <cfRule type="expression" priority="1" dxfId="5">
+  <conditionalFormatting sqref="A5:C520">
+    <cfRule type="expression" priority="1" dxfId="0">
       <formula>AND(MOD(ROW(),2)=0,$A5&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1710,60 +1486,60 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="24" t="inlineStr">
+      <c r="A1" s="19" t="inlineStr">
         <is>
           <t>Questions</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="27" t="inlineStr">
+      <c r="A2" s="22" t="inlineStr">
         <is>
           <t>Open questions IQ01-IQ35 (programme, integrations, infrastructure)</t>
         </is>
       </c>
     </row>
     <row r="3" ht="6" customHeight="1">
-      <c r="A3" s="28" t="n"/>
-      <c r="B3" s="28" t="n"/>
-      <c r="C3" s="28" t="n"/>
-      <c r="D3" s="28" t="n"/>
-      <c r="E3" s="28" t="n"/>
-      <c r="F3" s="28" t="n"/>
-      <c r="G3" s="28" t="n"/>
+      <c r="A3" s="23" t="n"/>
+      <c r="B3" s="23" t="n"/>
+      <c r="C3" s="23" t="n"/>
+      <c r="D3" s="23" t="n"/>
+      <c r="E3" s="23" t="n"/>
+      <c r="F3" s="23" t="n"/>
+      <c r="G3" s="23" t="n"/>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="29" t="inlineStr">
+      <c r="A4" s="24" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B4" s="29" t="inlineStr">
+      <c r="B4" s="24" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="C4" s="29" t="inlineStr">
+      <c r="C4" s="24" t="inlineStr">
         <is>
           <t>Topic</t>
         </is>
       </c>
-      <c r="D4" s="29" t="inlineStr">
+      <c r="D4" s="24" t="inlineStr">
         <is>
           <t>Question</t>
         </is>
       </c>
-      <c r="E4" s="29" t="inlineStr">
+      <c r="E4" s="24" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
-      <c r="F4" s="29" t="inlineStr">
+      <c r="F4" s="24" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="G4" s="29" t="inlineStr">
+      <c r="G4" s="24" t="inlineStr">
         <is>
           <t>BDOI answer</t>
         </is>
@@ -1785,7 +1561,7 @@
       </c>
       <c r="D5" s="12" t="inlineStr">
         <is>
-          <t>Which date in January 2028 is T? We propose Monday 3 January 2028, with the legacy freeze after the EOD of Wednesday 29 December 2027 and the legacy December / year-end close completed in legacy before the final extracts. If T is later in January, the migration rule "first business day of a month after a legacy month-end close" (DMQ25) no longer holds and the GL opening needs a January stub period.</t>
+          <t>Which date in January 2028 is T? We propose Monday 3 January 2028, with the legacy freeze after the EOD of Wednesday 29 December 2027 and the legacy December / year-end close completed in legacy before the final extracts. If T is later in January, the migration rule "first business day of a month after a legacy month-end close" (DMQ25) no longer holds and the GL opening needs a short January period.</t>
         </is>
       </c>
       <c r="E5" s="12" t="inlineStr">
@@ -1793,7 +1569,7 @@
           <t>Timeline slide; answer A1; DMQ25, DMQ18</t>
         </is>
       </c>
-      <c r="F5" s="30" t="inlineStr">
+      <c r="F5" s="25" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -1824,7 +1600,7 @@
           <t>Concept paper (superseded); answer A1; DMQ26</t>
         </is>
       </c>
-      <c r="F6" s="30" t="inlineStr">
+      <c r="F6" s="25" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -1855,7 +1631,7 @@
           <t>Concept paper VII, VIII, Annex C</t>
         </is>
       </c>
-      <c r="F7" s="30" t="inlineStr">
+      <c r="F7" s="25" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -1886,7 +1662,7 @@
           <t>Drop plan Drop 0; answer A2; UAM-NFR-11, 17, 19</t>
         </is>
       </c>
-      <c r="F8" s="30" t="inlineStr">
+      <c r="F8" s="25" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -1917,7 +1693,7 @@
           <t>Drop plan Drop 0; answer A2; BRD-11</t>
         </is>
       </c>
-      <c r="F9" s="30" t="inlineStr">
+      <c r="F9" s="25" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -1948,7 +1724,7 @@
           <t>Answer A2; BRRN.029; SP-SQ06</t>
         </is>
       </c>
-      <c r="F10" s="30" t="inlineStr">
+      <c r="F10" s="25" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -1979,7 +1755,7 @@
           <t>Drop plan; answer A2; Q11</t>
         </is>
       </c>
-      <c r="F11" s="30" t="inlineStr">
+      <c r="F11" s="25" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -2010,7 +1786,7 @@
           <t>Answer A2; BRD-12 p.4-5</t>
         </is>
       </c>
-      <c r="F12" s="30" t="inlineStr">
+      <c r="F12" s="25" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -2041,7 +1817,7 @@
           <t>Answer A2; OQ03; CSHID.008</t>
         </is>
       </c>
-      <c r="F13" s="30" t="inlineStr">
+      <c r="F13" s="25" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -2072,7 +1848,7 @@
           <t>Drop plan Drop 0; answer A2; AQ09, OQ03</t>
         </is>
       </c>
-      <c r="F14" s="30" t="inlineStr">
+      <c r="F14" s="25" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -2103,7 +1879,7 @@
           <t>Answer A2</t>
         </is>
       </c>
-      <c r="F15" s="30" t="inlineStr">
+      <c r="F15" s="25" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -2134,7 +1910,7 @@
           <t>Answer A2; Q12</t>
         </is>
       </c>
-      <c r="F16" s="30" t="inlineStr">
+      <c r="F16" s="25" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -2165,7 +1941,7 @@
           <t>Answers A2, A4</t>
         </is>
       </c>
-      <c r="F17" s="30" t="inlineStr">
+      <c r="F17" s="25" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -2196,7 +1972,7 @@
           <t>Answer A2; CSHID.008</t>
         </is>
       </c>
-      <c r="F18" s="30" t="inlineStr">
+      <c r="F18" s="25" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -2227,7 +2003,7 @@
           <t>Drop plan Drop 2; answer A2</t>
         </is>
       </c>
-      <c r="F19" s="30" t="inlineStr">
+      <c r="F19" s="25" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -2258,7 +2034,7 @@
           <t>Drop plan Drop 2; answer A2</t>
         </is>
       </c>
-      <c r="F20" s="30" t="inlineStr">
+      <c r="F20" s="25" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -2289,7 +2065,7 @@
           <t>Drop plan Drop 2</t>
         </is>
       </c>
-      <c r="F21" s="30" t="inlineStr">
+      <c r="F21" s="25" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -2320,7 +2096,7 @@
           <t>Drop plan Drop 2; Q06, OQ22</t>
         </is>
       </c>
-      <c r="F22" s="30" t="inlineStr">
+      <c r="F22" s="25" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -2351,7 +2127,7 @@
           <t>Drop plan Drop 2; answer A2; SQ01</t>
         </is>
       </c>
-      <c r="F23" s="30" t="inlineStr">
+      <c r="F23" s="25" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -2382,7 +2158,7 @@
           <t>Drop plan 1.D2, 1.D3; answer A3</t>
         </is>
       </c>
-      <c r="F24" s="30" t="inlineStr">
+      <c r="F24" s="25" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -2413,7 +2189,7 @@
           <t>Drop plan 2.1; BRD-4</t>
         </is>
       </c>
-      <c r="F25" s="30" t="inlineStr">
+      <c r="F25" s="25" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -2444,7 +2220,7 @@
           <t>Drop plan 2.4, 1.U6; BRD-8</t>
         </is>
       </c>
-      <c r="F26" s="30" t="inlineStr">
+      <c r="F26" s="25" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -2475,7 +2251,7 @@
           <t>Drop plan</t>
         </is>
       </c>
-      <c r="F27" s="30" t="inlineStr">
+      <c r="F27" s="25" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -2506,7 +2282,7 @@
           <t>Drop plan Drop 0</t>
         </is>
       </c>
-      <c r="F28" s="30" t="inlineStr">
+      <c r="F28" s="25" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -2529,7 +2305,7 @@
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>Please confirm that the IER describes BIBS as built: one backend (modular monolith) and one frontend on EKS, RDS PostgreSQL 16, ElastiCache Redis 7, MSK Kafka, S3; not the ten bv-* microservices, Aurora / MongoDB, Istio / OPA or EventBridge. Which edge is the BDO standard: ALB + WAF, CloudFront, Apigee X?</t>
+          <t>Please confirm that the IER describes the BIBS architecture: one backend (modular monolith) and one frontend on EKS, RDS PostgreSQL 16, ElastiCache Redis 7, MSK Kafka, S3; not the ten bv-* microservices, Aurora / MongoDB, Istio / OPA or EventBridge. Which edge is the BDO standard: ALB + WAF, CloudFront, Apigee X?</t>
         </is>
       </c>
       <c r="E29" s="12" t="inlineStr">
@@ -2537,7 +2313,7 @@
           <t>IER Architecture Diagram, K8s sheets</t>
         </is>
       </c>
-      <c r="F29" s="30" t="inlineStr">
+      <c r="F29" s="25" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -2568,7 +2344,7 @@
           <t>IER HW &amp; SW Requirements; hosting appendix; DCR-135</t>
         </is>
       </c>
-      <c r="F30" s="30" t="inlineStr">
+      <c r="F30" s="25" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -2599,7 +2375,7 @@
           <t>IER Assumptions 3</t>
         </is>
       </c>
-      <c r="F31" s="30" t="inlineStr">
+      <c r="F31" s="25" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -2630,7 +2406,7 @@
           <t>IER VDI Requirements; hosting appendix</t>
         </is>
       </c>
-      <c r="F32" s="30" t="inlineStr">
+      <c r="F32" s="25" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -2661,7 +2437,7 @@
           <t>IER sheets</t>
         </is>
       </c>
-      <c r="F33" s="30" t="inlineStr">
+      <c r="F33" s="25" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -2692,7 +2468,7 @@
           <t>IER sheets</t>
         </is>
       </c>
-      <c r="F34" s="30" t="inlineStr">
+      <c r="F34" s="25" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -2715,15 +2491,15 @@
       </c>
       <c r="D35" s="12" t="inlineStr">
         <is>
-          <t>Please confirm the five decisions of DOCUMENT_STORAGE_DECISION.md section 5: option C with 5-minute presigned links (or option B, streaming through BIBS); the malware scanning service; Object Lock mode and the records under legal hold; KMS key ownership and rotation; whether ECM receives copies of any record class. Also the bucket account and the DR region for replication.</t>
+          <t>Please confirm the five decisions of the document storage proposal (section 6.3): option C with 5-minute presigned links (or option B, streaming through BIBS); the malware scanning service; Object Lock mode and the records under legal hold; KMS key ownership and rotation; whether ECM receives copies of any record class. Also the bucket account and the DR region for replication.</t>
         </is>
       </c>
       <c r="E35" s="12" t="inlineStr">
         <is>
-          <t>Answer A4; DOCUMENT_STORAGE_DECISION.md</t>
-        </is>
-      </c>
-      <c r="F35" s="30" t="inlineStr">
+          <t>Answer A4; section 6.3</t>
+        </is>
+      </c>
+      <c r="F35" s="25" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -2754,7 +2530,7 @@
           <t>IER; DCR-166</t>
         </is>
       </c>
-      <c r="F36" s="30" t="inlineStr">
+      <c r="F36" s="25" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -2785,7 +2561,7 @@
           <t>IER Pre-Prod, K8s sheets</t>
         </is>
       </c>
-      <c r="F37" s="30" t="inlineStr">
+      <c r="F37" s="25" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -2808,7 +2584,7 @@
       </c>
       <c r="D38" s="12" t="inlineStr">
         <is>
-          <t>Please confirm cluster mode disabled (one shard, Multi-AZ replica) for Pre-Prod and PROD; "cluster" in the HW sheet would need a code change.</t>
+          <t>Please confirm cluster mode disabled (one shard, Multi-AZ replica) for Pre-Prod and PROD; "cluster" in the HW sheet would need a change in BIBS.</t>
         </is>
       </c>
       <c r="E38" s="12" t="inlineStr">
@@ -2816,7 +2592,7 @@
           <t>IER HW &amp; SW Requirements</t>
         </is>
       </c>
-      <c r="F38" s="30" t="inlineStr">
+      <c r="F38" s="25" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -2847,7 +2623,7 @@
           <t>Timeline slide</t>
         </is>
       </c>
-      <c r="F39" s="30" t="inlineStr">
+      <c r="F39" s="25" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -2860,24 +2636,24 @@
     <mergeCell ref="A2:G2"/>
   </mergeCells>
   <conditionalFormatting sqref="F5:F539">
-    <cfRule type="cellIs" priority="1" operator="equal" dxfId="2" stopIfTrue="1">
+    <cfRule type="cellIs" priority="1" operator="equal" dxfId="3" stopIfTrue="1">
       <formula>"OPEN"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="2" operator="equal" dxfId="0" stopIfTrue="1">
+    <cfRule type="cellIs" priority="2" operator="equal" dxfId="1" stopIfTrue="1">
       <formula>"ANSWERED"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="3" operator="equal" dxfId="0" stopIfTrue="1">
+    <cfRule type="cellIs" priority="3" operator="equal" dxfId="1" stopIfTrue="1">
       <formula>"CLOSED"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A5:G539">
-    <cfRule type="expression" priority="4" dxfId="5">
+    <cfRule type="expression" priority="4" dxfId="0">
       <formula>AND(MOD(ROW(),2)=0,$A5&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
     <dataValidation sqref="F5:F539" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Status" error="Choose a value from the list (Status)." type="list">
-      <formula1>'_lists'!$B$1:$B$3</formula1>
+      <formula1>'_lists'!$A$1:$A$3</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="1"/>
@@ -2900,17 +2676,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>FIT</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
           <t>OPEN</t>
         </is>
       </c>
@@ -2918,11 +2689,6 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CONFIGURE</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
           <t>ANSWERED</t>
         </is>
       </c>
@@ -2930,26 +2696,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CHANGE</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
           <t>CLOSED</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>OUT</t>
         </is>
       </c>
     </row>
@@ -2964,7 +2711,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D64"/>
+  <dimension ref="A1:D55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2974,14 +2721,14 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="24" t="inlineStr">
+      <c r="A1" s="19" t="inlineStr">
         <is>
           <t>README – columns of each sheet</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="23" t="inlineStr">
+      <c r="A2" s="18" t="inlineStr">
         <is>
           <t>BIBS Integration Inventory, version 1.0. Drop-down columns accept only the listed values.</t>
         </is>
@@ -3015,7 +2762,7 @@
           <t>Integrations</t>
         </is>
       </c>
-      <c r="B5" s="25" t="inlineStr">
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
@@ -3033,7 +2780,7 @@
           <t>Integrations</t>
         </is>
       </c>
-      <c r="B6" s="26" t="inlineStr">
+      <c r="B6" s="21" t="inlineStr">
         <is>
           <t>Integration</t>
         </is>
@@ -3051,7 +2798,7 @@
           <t>Integrations</t>
         </is>
       </c>
-      <c r="B7" s="25" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr">
         <is>
           <t>Drop</t>
         </is>
@@ -3069,7 +2816,7 @@
           <t>Integrations</t>
         </is>
       </c>
-      <c r="B8" s="26" t="inlineStr">
+      <c r="B8" s="21" t="inlineStr">
         <is>
           <t>BDOI meaning</t>
         </is>
@@ -3087,7 +2834,7 @@
           <t>Integrations</t>
         </is>
       </c>
-      <c r="B9" s="25" t="inlineStr">
+      <c r="B9" s="20" t="inlineStr">
         <is>
           <t>Our understanding (to confirm)</t>
         </is>
@@ -3105,7 +2852,7 @@
           <t>Integrations</t>
         </is>
       </c>
-      <c r="B10" s="26" t="inlineStr">
+      <c r="B10" s="21" t="inlineStr">
         <is>
           <t>Direction</t>
         </is>
@@ -3123,7 +2870,7 @@
           <t>Integrations</t>
         </is>
       </c>
-      <c r="B11" s="25" t="inlineStr">
+      <c r="B11" s="20" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
@@ -3141,14 +2888,14 @@
           <t>Integrations</t>
         </is>
       </c>
-      <c r="B12" s="26" t="inlineStr">
-        <is>
-          <t>BIBS module</t>
+      <c r="B12" s="21" t="inlineStr">
+        <is>
+          <t>Open points</t>
         </is>
       </c>
       <c r="C12" s="14" t="inlineStr">
         <is>
-          <t>Module(s) that own the interface</t>
+          <t>What BDOI IT still has to specify</t>
         </is>
       </c>
       <c r="D12" s="14" t="inlineStr"/>
@@ -3159,14 +2906,14 @@
           <t>Integrations</t>
         </is>
       </c>
-      <c r="B13" s="25" t="inlineStr">
-        <is>
-          <t>Existing seam in BIBS</t>
+      <c r="B13" s="20" t="inlineStr">
+        <is>
+          <t>Questions</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>Port, handler or mechanism in the code today</t>
+          <t>IQ questions of this document</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr"/>
@@ -3174,39 +2921,35 @@
     <row r="14">
       <c r="A14" s="14" t="inlineStr">
         <is>
-          <t>Integrations</t>
-        </is>
-      </c>
-      <c r="B14" s="26" t="inlineStr">
-        <is>
-          <t>Fit</t>
+          <t>Other interfaces</t>
+        </is>
+      </c>
+      <c r="B14" s="21" t="inlineStr">
+        <is>
+          <t>Interface</t>
         </is>
       </c>
       <c r="C14" s="14" t="inlineStr">
         <is>
-          <t>FIT / CONFIGURE / CHANGE / NEW / OUT</t>
-        </is>
-      </c>
-      <c r="D14" s="14" t="inlineStr">
-        <is>
-          <t>FIT, CONFIGURE, CHANGE, NEW, OUT</t>
-        </is>
-      </c>
+          <t>Interface named in a BRD</t>
+        </is>
+      </c>
+      <c r="D14" s="14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>Integrations</t>
-        </is>
-      </c>
-      <c r="B15" s="25" t="inlineStr">
-        <is>
-          <t>Build needed</t>
+          <t>Other interfaces</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
+        <is>
+          <t>Named in</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>What must be built or configured</t>
+          <t>BRD and requirement</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr"/>
@@ -3214,17 +2957,17 @@
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
         <is>
-          <t>Integrations</t>
-        </is>
-      </c>
-      <c r="B16" s="26" t="inlineStr">
-        <is>
-          <t>Open points</t>
+          <t>Other interfaces</t>
+        </is>
+      </c>
+      <c r="B16" s="21" t="inlineStr">
+        <is>
+          <t>To confirm</t>
         </is>
       </c>
       <c r="C16" s="14" t="inlineStr">
         <is>
-          <t>What BDOI IT still has to specify</t>
+          <t>What BDOI confirms</t>
         </is>
       </c>
       <c r="D16" s="14" t="inlineStr"/>
@@ -3232,17 +2975,17 @@
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
         <is>
-          <t>Integrations</t>
-        </is>
-      </c>
-      <c r="B17" s="25" t="inlineStr">
-        <is>
-          <t>Questions</t>
+          <t>Drop map</t>
+        </is>
+      </c>
+      <c r="B17" s="20" t="inlineStr">
+        <is>
+          <t>Drop</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>IQ questions of this document</t>
+          <t>Drop of the BDOI plan</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr"/>
@@ -3250,17 +2993,17 @@
     <row r="18">
       <c r="A18" s="14" t="inlineStr">
         <is>
-          <t>Other interfaces</t>
-        </is>
-      </c>
-      <c r="B18" s="26" t="inlineStr">
-        <is>
-          <t>Interface</t>
+          <t>Drop map</t>
+        </is>
+      </c>
+      <c r="B18" s="21" t="inlineStr">
+        <is>
+          <t>#</t>
         </is>
       </c>
       <c r="C18" s="14" t="inlineStr">
         <is>
-          <t>Interface named in a BRD</t>
+          <t>Line item</t>
         </is>
       </c>
       <c r="D18" s="14" t="inlineStr"/>
@@ -3268,17 +3011,17 @@
     <row r="19">
       <c r="A19" s="12" t="inlineStr">
         <is>
-          <t>Other interfaces</t>
-        </is>
-      </c>
-      <c r="B19" s="25" t="inlineStr">
-        <is>
-          <t>Named in</t>
+          <t>Drop map</t>
+        </is>
+      </c>
+      <c r="B19" s="20" t="inlineStr">
+        <is>
+          <t>Drop item</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>BRD and requirement</t>
+          <t>Module / functionality on the slide</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr"/>
@@ -3286,17 +3029,17 @@
     <row r="20">
       <c r="A20" s="14" t="inlineStr">
         <is>
-          <t>Other interfaces</t>
-        </is>
-      </c>
-      <c r="B20" s="26" t="inlineStr">
-        <is>
-          <t>BIBS seam</t>
+          <t>Drop map</t>
+        </is>
+      </c>
+      <c r="B20" s="21" t="inlineStr">
+        <is>
+          <t>BRD named by BDOI</t>
         </is>
       </c>
       <c r="C20" s="14" t="inlineStr">
         <is>
-          <t>Mechanism in BIBS</t>
+          <t>BRD file column of the slide</t>
         </is>
       </c>
       <c r="D20" s="14" t="inlineStr"/>
@@ -3304,17 +3047,17 @@
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
         <is>
-          <t>Other interfaces</t>
-        </is>
-      </c>
-      <c r="B21" s="25" t="inlineStr">
-        <is>
-          <t>To confirm</t>
+          <t>Drop map</t>
+        </is>
+      </c>
+      <c r="B21" s="20" t="inlineStr">
+        <is>
+          <t>BIBS BRD</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>What BDOI confirms</t>
+          <t>BIBS BRD number(s)</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr"/>
@@ -3325,14 +3068,14 @@
           <t>Drop map</t>
         </is>
       </c>
-      <c r="B22" s="26" t="inlineStr">
-        <is>
-          <t>Drop</t>
+      <c r="B22" s="21" t="inlineStr">
+        <is>
+          <t>FRS</t>
         </is>
       </c>
       <c r="C22" s="14" t="inlineStr">
         <is>
-          <t>Drop of the BDOI plan</t>
+          <t>FRS and requirement prefix</t>
         </is>
       </c>
       <c r="D22" s="14" t="inlineStr"/>
@@ -3343,14 +3086,14 @@
           <t>Drop map</t>
         </is>
       </c>
-      <c r="B23" s="25" t="inlineStr">
-        <is>
-          <t>#</t>
+      <c r="B23" s="20" t="inlineStr">
+        <is>
+          <t>Gap or mismatch</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>Line item</t>
+          <t>Observation</t>
         </is>
       </c>
       <c r="D23" s="12" t="inlineStr"/>
@@ -3361,14 +3104,14 @@
           <t>Drop map</t>
         </is>
       </c>
-      <c r="B24" s="26" t="inlineStr">
-        <is>
-          <t>Drop item</t>
+      <c r="B24" s="21" t="inlineStr">
+        <is>
+          <t>Refs</t>
         </is>
       </c>
       <c r="C24" s="14" t="inlineStr">
         <is>
-          <t>Module / functionality on the slide</t>
+          <t>Questions and register</t>
         </is>
       </c>
       <c r="D24" s="14" t="inlineStr"/>
@@ -3376,17 +3119,17 @@
     <row r="25">
       <c r="A25" s="12" t="inlineStr">
         <is>
-          <t>Drop map</t>
-        </is>
-      </c>
-      <c r="B25" s="25" t="inlineStr">
-        <is>
-          <t>BRD named by BDOI</t>
+          <t>Documents by drop</t>
+        </is>
+      </c>
+      <c r="B25" s="20" t="inlineStr">
+        <is>
+          <t>Document</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>BRD file column of the slide</t>
+          <t>BRD or collateral</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr"/>
@@ -3394,17 +3137,17 @@
     <row r="26">
       <c r="A26" s="14" t="inlineStr">
         <is>
-          <t>Drop map</t>
-        </is>
-      </c>
-      <c r="B26" s="26" t="inlineStr">
-        <is>
-          <t>BIBS BRD</t>
+          <t>Documents by drop</t>
+        </is>
+      </c>
+      <c r="B26" s="21" t="inlineStr">
+        <is>
+          <t>Kind</t>
         </is>
       </c>
       <c r="C26" s="14" t="inlineStr">
         <is>
-          <t>BIBS BRD number(s)</t>
+          <t>FRS, test plan, ...</t>
         </is>
       </c>
       <c r="D26" s="14" t="inlineStr"/>
@@ -3412,17 +3155,17 @@
     <row r="27">
       <c r="A27" s="12" t="inlineStr">
         <is>
-          <t>Drop map</t>
-        </is>
-      </c>
-      <c r="B27" s="25" t="inlineStr">
-        <is>
-          <t>FRS</t>
+          <t>Documents by drop</t>
+        </is>
+      </c>
+      <c r="B27" s="20" t="inlineStr">
+        <is>
+          <t>File</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>FRS and requirement prefix</t>
+          <t>Output file(s)</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr"/>
@@ -3430,17 +3173,17 @@
     <row r="28">
       <c r="A28" s="14" t="inlineStr">
         <is>
-          <t>Drop map</t>
-        </is>
-      </c>
-      <c r="B28" s="26" t="inlineStr">
-        <is>
-          <t>BIBS modules and screens</t>
+          <t>Documents by drop</t>
+        </is>
+      </c>
+      <c r="B28" s="21" t="inlineStr">
+        <is>
+          <t>Drop (folder)</t>
         </is>
       </c>
       <c r="C28" s="14" t="inlineStr">
         <is>
-          <t>Where it is in BIBS</t>
+          <t>Folder of the restructure</t>
         </is>
       </c>
       <c r="D28" s="14" t="inlineStr"/>
@@ -3448,17 +3191,17 @@
     <row r="29">
       <c r="A29" s="12" t="inlineStr">
         <is>
-          <t>Drop map</t>
-        </is>
-      </c>
-      <c r="B29" s="25" t="inlineStr">
-        <is>
-          <t>Status</t>
+          <t>Documents by drop</t>
+        </is>
+      </c>
+      <c r="B29" s="20" t="inlineStr">
+        <is>
+          <t>Shared with</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>Built / Being built / Designed / Mixed</t>
+          <t>Other drops that use it</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr"/>
@@ -3466,17 +3209,17 @@
     <row r="30">
       <c r="A30" s="14" t="inlineStr">
         <is>
-          <t>Drop map</t>
-        </is>
-      </c>
-      <c r="B30" s="26" t="inlineStr">
-        <is>
-          <t>Gap or mismatch</t>
+          <t>Documents by drop</t>
+        </is>
+      </c>
+      <c r="B30" s="21" t="inlineStr">
+        <is>
+          <t>Note</t>
         </is>
       </c>
       <c r="C30" s="14" t="inlineStr">
         <is>
-          <t>Observation</t>
+          <t>Note</t>
         </is>
       </c>
       <c r="D30" s="14" t="inlineStr"/>
@@ -3484,17 +3227,17 @@
     <row r="31">
       <c r="A31" s="12" t="inlineStr">
         <is>
-          <t>Drop map</t>
-        </is>
-      </c>
-      <c r="B31" s="25" t="inlineStr">
-        <is>
-          <t>Refs</t>
+          <t>Infrastructure</t>
+        </is>
+      </c>
+      <c r="B31" s="20" t="inlineStr">
+        <is>
+          <t>Topic</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>Questions and register</t>
+          <t>Area</t>
         </is>
       </c>
       <c r="D31" s="12" t="inlineStr"/>
@@ -3502,17 +3245,17 @@
     <row r="32">
       <c r="A32" s="14" t="inlineStr">
         <is>
-          <t>Documents by drop</t>
-        </is>
-      </c>
-      <c r="B32" s="26" t="inlineStr">
-        <is>
-          <t>Document</t>
+          <t>Infrastructure</t>
+        </is>
+      </c>
+      <c r="B32" s="21" t="inlineStr">
+        <is>
+          <t>IER (BDOI IT)</t>
         </is>
       </c>
       <c r="C32" s="14" t="inlineStr">
         <is>
-          <t>BRD or collateral</t>
+          <t>What the IER workbook states</t>
         </is>
       </c>
       <c r="D32" s="14" t="inlineStr"/>
@@ -3520,17 +3263,17 @@
     <row r="33">
       <c r="A33" s="12" t="inlineStr">
         <is>
-          <t>Documents by drop</t>
-        </is>
-      </c>
-      <c r="B33" s="25" t="inlineStr">
-        <is>
-          <t>Kind</t>
+          <t>Infrastructure</t>
+        </is>
+      </c>
+      <c r="B33" s="20" t="inlineStr">
+        <is>
+          <t>BIBS</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>FRS, test plan, ...</t>
+          <t>BIBS architecture and deployment</t>
         </is>
       </c>
       <c r="D33" s="12" t="inlineStr"/>
@@ -3538,17 +3281,17 @@
     <row r="34">
       <c r="A34" s="14" t="inlineStr">
         <is>
-          <t>Documents by drop</t>
-        </is>
-      </c>
-      <c r="B34" s="26" t="inlineStr">
-        <is>
-          <t>File</t>
+          <t>Infrastructure</t>
+        </is>
+      </c>
+      <c r="B34" s="21" t="inlineStr">
+        <is>
+          <t>Assessment</t>
         </is>
       </c>
       <c r="C34" s="14" t="inlineStr">
         <is>
-          <t>Output file(s)</t>
+          <t>Aligned / Mismatch / Gap</t>
         </is>
       </c>
       <c r="D34" s="14" t="inlineStr"/>
@@ -3556,17 +3299,17 @@
     <row r="35">
       <c r="A35" s="12" t="inlineStr">
         <is>
-          <t>Documents by drop</t>
-        </is>
-      </c>
-      <c r="B35" s="25" t="inlineStr">
-        <is>
-          <t>Drop (folder)</t>
+          <t>Infrastructure</t>
+        </is>
+      </c>
+      <c r="B35" s="20" t="inlineStr">
+        <is>
+          <t>Change needed</t>
         </is>
       </c>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>Folder of the restructure</t>
+          <t>Change in the IER or in BIBS</t>
         </is>
       </c>
       <c r="D35" s="12" t="inlineStr"/>
@@ -3574,17 +3317,17 @@
     <row r="36">
       <c r="A36" s="14" t="inlineStr">
         <is>
-          <t>Documents by drop</t>
-        </is>
-      </c>
-      <c r="B36" s="26" t="inlineStr">
-        <is>
-          <t>Shared with</t>
+          <t>Infrastructure</t>
+        </is>
+      </c>
+      <c r="B36" s="21" t="inlineStr">
+        <is>
+          <t>Ref</t>
         </is>
       </c>
       <c r="C36" s="14" t="inlineStr">
         <is>
-          <t>Other drops that use it</t>
+          <t>Register, IQ</t>
         </is>
       </c>
       <c r="D36" s="14" t="inlineStr"/>
@@ -3592,17 +3335,17 @@
     <row r="37">
       <c r="A37" s="12" t="inlineStr">
         <is>
-          <t>Documents by drop</t>
-        </is>
-      </c>
-      <c r="B37" s="25" t="inlineStr">
-        <is>
-          <t>Note</t>
+          <t>S3 documents</t>
+        </is>
+      </c>
+      <c r="B37" s="20" t="inlineStr">
+        <is>
+          <t>Area</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>Note</t>
+          <t>What is stored</t>
         </is>
       </c>
       <c r="D37" s="12" t="inlineStr"/>
@@ -3610,17 +3353,17 @@
     <row r="38">
       <c r="A38" s="14" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
-        </is>
-      </c>
-      <c r="B38" s="26" t="inlineStr">
-        <is>
-          <t>Topic</t>
+          <t>S3 documents</t>
+        </is>
+      </c>
+      <c r="B38" s="21" t="inlineStr">
+        <is>
+          <t>Proposal</t>
         </is>
       </c>
       <c r="C38" s="14" t="inlineStr">
         <is>
-          <t>Area</t>
+          <t>S3-only storage (answer A4)</t>
         </is>
       </c>
       <c r="D38" s="14" t="inlineStr"/>
@@ -3628,17 +3371,17 @@
     <row r="39">
       <c r="A39" s="12" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
-        </is>
-      </c>
-      <c r="B39" s="25" t="inlineStr">
-        <is>
-          <t>IER (BDOI IT)</t>
+          <t>K8s sizing</t>
+        </is>
+      </c>
+      <c r="B39" s="20" t="inlineStr">
+        <is>
+          <t>Environment</t>
         </is>
       </c>
       <c r="C39" s="12" t="inlineStr">
         <is>
-          <t>What the IER workbook states</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="D39" s="12" t="inlineStr"/>
@@ -3646,17 +3389,17 @@
     <row r="40">
       <c r="A40" s="14" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
-        </is>
-      </c>
-      <c r="B40" s="26" t="inlineStr">
-        <is>
-          <t>BIBS as built</t>
+          <t>K8s sizing</t>
+        </is>
+      </c>
+      <c r="B40" s="21" t="inlineStr">
+        <is>
+          <t>Deployment</t>
         </is>
       </c>
       <c r="C40" s="14" t="inlineStr">
         <is>
-          <t>Code, deployment files, architecture documents</t>
+          <t>Kubernetes deployment</t>
         </is>
       </c>
       <c r="D40" s="14" t="inlineStr"/>
@@ -3664,17 +3407,17 @@
     <row r="41">
       <c r="A41" s="12" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
-        </is>
-      </c>
-      <c r="B41" s="25" t="inlineStr">
-        <is>
-          <t>Assessment</t>
+          <t>K8s sizing</t>
+        </is>
+      </c>
+      <c r="B41" s="20" t="inlineStr">
+        <is>
+          <t>Min replicas</t>
         </is>
       </c>
       <c r="C41" s="12" t="inlineStr">
         <is>
-          <t>Aligned / Mismatch / Gap</t>
+          <t>HPA minimum</t>
         </is>
       </c>
       <c r="D41" s="12" t="inlineStr"/>
@@ -3682,17 +3425,17 @@
     <row r="42">
       <c r="A42" s="14" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
-        </is>
-      </c>
-      <c r="B42" s="26" t="inlineStr">
-        <is>
-          <t>Change needed</t>
+          <t>K8s sizing</t>
+        </is>
+      </c>
+      <c r="B42" s="21" t="inlineStr">
+        <is>
+          <t>Max replicas</t>
         </is>
       </c>
       <c r="C42" s="14" t="inlineStr">
         <is>
-          <t>Change in the IER or in BIBS</t>
+          <t>HPA maximum</t>
         </is>
       </c>
       <c r="D42" s="14" t="inlineStr"/>
@@ -3700,17 +3443,17 @@
     <row r="43">
       <c r="A43" s="12" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
-        </is>
-      </c>
-      <c r="B43" s="25" t="inlineStr">
-        <is>
-          <t>Ref</t>
+          <t>K8s sizing</t>
+        </is>
+      </c>
+      <c r="B43" s="20" t="inlineStr">
+        <is>
+          <t>Requests CPU / memory</t>
         </is>
       </c>
       <c r="C43" s="12" t="inlineStr">
         <is>
-          <t>Register, IQ</t>
+          <t>Per pod</t>
         </is>
       </c>
       <c r="D43" s="12" t="inlineStr"/>
@@ -3718,17 +3461,17 @@
     <row r="44">
       <c r="A44" s="14" t="inlineStr">
         <is>
-          <t>S3 changes</t>
-        </is>
-      </c>
-      <c r="B44" s="26" t="inlineStr">
-        <is>
-          <t>Area</t>
+          <t>K8s sizing</t>
+        </is>
+      </c>
+      <c r="B44" s="21" t="inlineStr">
+        <is>
+          <t>Limits CPU / memory</t>
         </is>
       </c>
       <c r="C44" s="14" t="inlineStr">
         <is>
-          <t>What is stored</t>
+          <t>Per pod</t>
         </is>
       </c>
       <c r="D44" s="14" t="inlineStr"/>
@@ -3736,17 +3479,17 @@
     <row r="45">
       <c r="A45" s="12" t="inlineStr">
         <is>
-          <t>S3 changes</t>
-        </is>
-      </c>
-      <c r="B45" s="25" t="inlineStr">
-        <is>
-          <t>Today</t>
+          <t>K8s sizing</t>
+        </is>
+      </c>
+      <c r="B45" s="20" t="inlineStr">
+        <is>
+          <t>Note</t>
         </is>
       </c>
       <c r="C45" s="12" t="inlineStr">
         <is>
-          <t>Tables and classes</t>
+          <t>Note</t>
         </is>
       </c>
       <c r="D45" s="12" t="inlineStr"/>
@@ -3754,17 +3497,17 @@
     <row r="46">
       <c r="A46" s="14" t="inlineStr">
         <is>
-          <t>S3 changes</t>
-        </is>
-      </c>
-      <c r="B46" s="26" t="inlineStr">
-        <is>
-          <t>Change</t>
+          <t>Timeline</t>
+        </is>
+      </c>
+      <c r="B46" s="21" t="inlineStr">
+        <is>
+          <t>Stream</t>
         </is>
       </c>
       <c r="C46" s="14" t="inlineStr">
         <is>
-          <t>Change for S3-only storage (answer A4)</t>
+          <t>Timeline bar</t>
         </is>
       </c>
       <c r="D46" s="14" t="inlineStr"/>
@@ -3772,17 +3515,17 @@
     <row r="47">
       <c r="A47" s="12" t="inlineStr">
         <is>
-          <t>K8s sizing</t>
-        </is>
-      </c>
-      <c r="B47" s="25" t="inlineStr">
-        <is>
-          <t>Environment</t>
+          <t>Timeline</t>
+        </is>
+      </c>
+      <c r="B47" s="20" t="inlineStr">
+        <is>
+          <t>BDOI window</t>
         </is>
       </c>
       <c r="C47" s="12" t="inlineStr">
         <is>
-          <t>Environment</t>
+          <t>From the slide</t>
         </is>
       </c>
       <c r="D47" s="12" t="inlineStr"/>
@@ -3790,17 +3533,17 @@
     <row r="48">
       <c r="A48" s="14" t="inlineStr">
         <is>
-          <t>K8s sizing</t>
-        </is>
-      </c>
-      <c r="B48" s="26" t="inlineStr">
-        <is>
-          <t>Deployment</t>
+          <t>Timeline</t>
+        </is>
+      </c>
+      <c r="B48" s="21" t="inlineStr">
+        <is>
+          <t>What we deliver, by when</t>
         </is>
       </c>
       <c r="C48" s="14" t="inlineStr">
         <is>
-          <t>Kubernetes deployment</t>
+          <t>Plan</t>
         </is>
       </c>
       <c r="D48" s="14" t="inlineStr"/>
@@ -3808,17 +3551,17 @@
     <row r="49">
       <c r="A49" s="12" t="inlineStr">
         <is>
-          <t>K8s sizing</t>
-        </is>
-      </c>
-      <c r="B49" s="25" t="inlineStr">
-        <is>
-          <t>Min replicas</t>
+          <t>Questions</t>
+        </is>
+      </c>
+      <c r="B49" s="20" t="inlineStr">
+        <is>
+          <t>ID</t>
         </is>
       </c>
       <c r="C49" s="12" t="inlineStr">
         <is>
-          <t>HPA minimum</t>
+          <t>IQ question</t>
         </is>
       </c>
       <c r="D49" s="12" t="inlineStr"/>
@@ -3826,17 +3569,17 @@
     <row r="50">
       <c r="A50" s="14" t="inlineStr">
         <is>
-          <t>K8s sizing</t>
-        </is>
-      </c>
-      <c r="B50" s="26" t="inlineStr">
-        <is>
-          <t>Max replicas</t>
+          <t>Questions</t>
+        </is>
+      </c>
+      <c r="B50" s="21" t="inlineStr">
+        <is>
+          <t>Priority</t>
         </is>
       </c>
       <c r="C50" s="14" t="inlineStr">
         <is>
-          <t>HPA maximum</t>
+          <t>1 = answer by 16 Oct 2026</t>
         </is>
       </c>
       <c r="D50" s="14" t="inlineStr"/>
@@ -3844,17 +3587,17 @@
     <row r="51">
       <c r="A51" s="12" t="inlineStr">
         <is>
-          <t>K8s sizing</t>
-        </is>
-      </c>
-      <c r="B51" s="25" t="inlineStr">
-        <is>
-          <t>Requests CPU / memory</t>
+          <t>Questions</t>
+        </is>
+      </c>
+      <c r="B51" s="20" t="inlineStr">
+        <is>
+          <t>Topic</t>
         </is>
       </c>
       <c r="C51" s="12" t="inlineStr">
         <is>
-          <t>Per pod</t>
+          <t>Topic</t>
         </is>
       </c>
       <c r="D51" s="12" t="inlineStr"/>
@@ -3862,17 +3605,17 @@
     <row r="52">
       <c r="A52" s="14" t="inlineStr">
         <is>
-          <t>K8s sizing</t>
-        </is>
-      </c>
-      <c r="B52" s="26" t="inlineStr">
-        <is>
-          <t>Limits CPU / memory</t>
+          <t>Questions</t>
+        </is>
+      </c>
+      <c r="B52" s="21" t="inlineStr">
+        <is>
+          <t>Question</t>
         </is>
       </c>
       <c r="C52" s="14" t="inlineStr">
         <is>
-          <t>Per pod</t>
+          <t>Question to BDOI</t>
         </is>
       </c>
       <c r="D52" s="14" t="inlineStr"/>
@@ -3880,17 +3623,17 @@
     <row r="53">
       <c r="A53" s="12" t="inlineStr">
         <is>
-          <t>K8s sizing</t>
-        </is>
-      </c>
-      <c r="B53" s="25" t="inlineStr">
-        <is>
-          <t>Note</t>
+          <t>Questions</t>
+        </is>
+      </c>
+      <c r="B53" s="20" t="inlineStr">
+        <is>
+          <t>Source</t>
         </is>
       </c>
       <c r="C53" s="12" t="inlineStr">
         <is>
-          <t>Note</t>
+          <t>Where it comes from</t>
         </is>
       </c>
       <c r="D53" s="12" t="inlineStr"/>
@@ -3898,207 +3641,45 @@
     <row r="54">
       <c r="A54" s="14" t="inlineStr">
         <is>
-          <t>Timeline</t>
-        </is>
-      </c>
-      <c r="B54" s="26" t="inlineStr">
-        <is>
-          <t>Stream</t>
+          <t>Questions</t>
+        </is>
+      </c>
+      <c r="B54" s="21" t="inlineStr">
+        <is>
+          <t>Status</t>
         </is>
       </c>
       <c r="C54" s="14" t="inlineStr">
         <is>
-          <t>Timeline bar</t>
-        </is>
-      </c>
-      <c r="D54" s="14" t="inlineStr"/>
+          <t>Open / Answered</t>
+        </is>
+      </c>
+      <c r="D54" s="14" t="inlineStr">
+        <is>
+          <t>OPEN, ANSWERED, CLOSED</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="12" t="inlineStr">
         <is>
-          <t>Timeline</t>
-        </is>
-      </c>
-      <c r="B55" s="25" t="inlineStr">
-        <is>
-          <t>BDOI window</t>
+          <t>Questions</t>
+        </is>
+      </c>
+      <c r="B55" s="20" t="inlineStr">
+        <is>
+          <t>BDOI answer</t>
         </is>
       </c>
       <c r="C55" s="12" t="inlineStr">
         <is>
-          <t>From the slide</t>
+          <t>Filled by BDOI</t>
         </is>
       </c>
       <c r="D55" s="12" t="inlineStr"/>
     </row>
-    <row r="56">
-      <c r="A56" s="14" t="inlineStr">
-        <is>
-          <t>Timeline</t>
-        </is>
-      </c>
-      <c r="B56" s="26" t="inlineStr">
-        <is>
-          <t>Status today</t>
-        </is>
-      </c>
-      <c r="C56" s="14" t="inlineStr">
-        <is>
-          <t>BIBS status</t>
-        </is>
-      </c>
-      <c r="D56" s="14" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="12" t="inlineStr">
-        <is>
-          <t>Timeline</t>
-        </is>
-      </c>
-      <c r="B57" s="25" t="inlineStr">
-        <is>
-          <t>What we deliver, by when</t>
-        </is>
-      </c>
-      <c r="C57" s="12" t="inlineStr">
-        <is>
-          <t>Plan</t>
-        </is>
-      </c>
-      <c r="D57" s="12" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="14" t="inlineStr">
-        <is>
-          <t>Questions</t>
-        </is>
-      </c>
-      <c r="B58" s="26" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="C58" s="14" t="inlineStr">
-        <is>
-          <t>IQ question</t>
-        </is>
-      </c>
-      <c r="D58" s="14" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="12" t="inlineStr">
-        <is>
-          <t>Questions</t>
-        </is>
-      </c>
-      <c r="B59" s="25" t="inlineStr">
-        <is>
-          <t>Priority</t>
-        </is>
-      </c>
-      <c r="C59" s="12" t="inlineStr">
-        <is>
-          <t>1 = answer by 16 Oct 2026</t>
-        </is>
-      </c>
-      <c r="D59" s="12" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="14" t="inlineStr">
-        <is>
-          <t>Questions</t>
-        </is>
-      </c>
-      <c r="B60" s="26" t="inlineStr">
-        <is>
-          <t>Topic</t>
-        </is>
-      </c>
-      <c r="C60" s="14" t="inlineStr">
-        <is>
-          <t>Topic</t>
-        </is>
-      </c>
-      <c r="D60" s="14" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="12" t="inlineStr">
-        <is>
-          <t>Questions</t>
-        </is>
-      </c>
-      <c r="B61" s="25" t="inlineStr">
-        <is>
-          <t>Question</t>
-        </is>
-      </c>
-      <c r="C61" s="12" t="inlineStr">
-        <is>
-          <t>Question to BDOI</t>
-        </is>
-      </c>
-      <c r="D61" s="12" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="14" t="inlineStr">
-        <is>
-          <t>Questions</t>
-        </is>
-      </c>
-      <c r="B62" s="26" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="C62" s="14" t="inlineStr">
-        <is>
-          <t>Where it comes from</t>
-        </is>
-      </c>
-      <c r="D62" s="14" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="12" t="inlineStr">
-        <is>
-          <t>Questions</t>
-        </is>
-      </c>
-      <c r="B63" s="25" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="C63" s="12" t="inlineStr">
-        <is>
-          <t>Open / Answered</t>
-        </is>
-      </c>
-      <c r="D63" s="12" t="inlineStr">
-        <is>
-          <t>OPEN, ANSWERED, CLOSED</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="14" t="inlineStr">
-        <is>
-          <t>Questions</t>
-        </is>
-      </c>
-      <c r="B64" s="26" t="inlineStr">
-        <is>
-          <t>BDOI answer</t>
-        </is>
-      </c>
-      <c r="C64" s="14" t="inlineStr">
-        <is>
-          <t>Filled by BDOI</t>
-        </is>
-      </c>
-      <c r="D64" s="14" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A4:D64"/>
+  <autoFilter ref="A4:D55"/>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
@@ -4119,7 +3700,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M24"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -4129,105 +3710,77 @@
     <col width="42" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="30" customWidth="1" min="7" max="7"/>
-    <col width="24" customWidth="1" min="8" max="8"/>
-    <col width="42" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
-    <col width="40" customWidth="1" min="11" max="11"/>
-    <col width="30" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="30" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="24" t="inlineStr">
+      <c r="A1" s="19" t="inlineStr">
         <is>
           <t>Integrations</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="27" t="inlineStr">
+      <c r="A2" s="22" t="inlineStr">
         <is>
           <t>One row per integration named on the drop plan or by BDOI</t>
         </is>
       </c>
     </row>
     <row r="3" ht="6" customHeight="1">
-      <c r="A3" s="28" t="n"/>
-      <c r="B3" s="28" t="n"/>
-      <c r="C3" s="28" t="n"/>
-      <c r="D3" s="28" t="n"/>
-      <c r="E3" s="28" t="n"/>
-      <c r="F3" s="28" t="n"/>
-      <c r="G3" s="28" t="n"/>
-      <c r="H3" s="28" t="n"/>
-      <c r="I3" s="28" t="n"/>
-      <c r="J3" s="28" t="n"/>
-      <c r="K3" s="28" t="n"/>
-      <c r="L3" s="28" t="n"/>
-      <c r="M3" s="28" t="n"/>
+      <c r="A3" s="23" t="n"/>
+      <c r="B3" s="23" t="n"/>
+      <c r="C3" s="23" t="n"/>
+      <c r="D3" s="23" t="n"/>
+      <c r="E3" s="23" t="n"/>
+      <c r="F3" s="23" t="n"/>
+      <c r="G3" s="23" t="n"/>
+      <c r="H3" s="23" t="n"/>
+      <c r="I3" s="23" t="n"/>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="29" t="inlineStr">
+      <c r="A4" s="24" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B4" s="29" t="inlineStr">
+      <c r="B4" s="24" t="inlineStr">
         <is>
           <t>Integration</t>
         </is>
       </c>
-      <c r="C4" s="29" t="inlineStr">
+      <c r="C4" s="24" t="inlineStr">
         <is>
           <t>Drop</t>
         </is>
       </c>
-      <c r="D4" s="29" t="inlineStr">
+      <c r="D4" s="24" t="inlineStr">
         <is>
           <t>BDOI meaning</t>
         </is>
       </c>
-      <c r="E4" s="29" t="inlineStr">
+      <c r="E4" s="24" t="inlineStr">
         <is>
           <t>Our understanding (to confirm)</t>
         </is>
       </c>
-      <c r="F4" s="29" t="inlineStr">
+      <c r="F4" s="24" t="inlineStr">
         <is>
           <t>Direction</t>
         </is>
       </c>
-      <c r="G4" s="29" t="inlineStr">
+      <c r="G4" s="24" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="H4" s="29" t="inlineStr">
-        <is>
-          <t>BIBS module</t>
-        </is>
-      </c>
-      <c r="I4" s="29" t="inlineStr">
-        <is>
-          <t>Existing seam in BIBS</t>
-        </is>
-      </c>
-      <c r="J4" s="29" t="inlineStr">
-        <is>
-          <t>Fit</t>
-        </is>
-      </c>
-      <c r="K4" s="29" t="inlineStr">
-        <is>
-          <t>Build needed</t>
-        </is>
-      </c>
-      <c r="L4" s="29" t="inlineStr">
+      <c r="H4" s="24" t="inlineStr">
         <is>
           <t>Open points</t>
         </is>
       </c>
-      <c r="M4" s="29" t="inlineStr">
+      <c r="I4" s="24" t="inlineStr">
         <is>
           <t>Questions</t>
         </is>
@@ -4271,30 +3824,10 @@
       </c>
       <c r="H5" s="12" t="inlineStr">
         <is>
-          <t>security; Setup &amp; Administration &gt; Users</t>
+          <t>Protocol and claims, MFA and conditional access, session life against the 30-minute inactivity rule, non-BDO users</t>
         </is>
       </c>
       <c r="I5" s="12" t="inlineStr">
-        <is>
-          <t>security.service.directory.DirectoryAuthenticator (password check, LOCAL default; AUTH_MODE); SsoTokenExchange designed, not built (USER_ACCESS_DESIGN section 10)</t>
-        </is>
-      </c>
-      <c r="J5" s="30" t="inlineStr">
-        <is>
-          <t>CHANGE</t>
-        </is>
-      </c>
-      <c r="K5" s="12" t="inlineStr">
-        <is>
-          <t>OIDC log-in (frontend redirect, backend token validation with Spring Security OAuth2), user mapping by sec_user.windows_id or UPN, log-out to Entra, local break-glass administrator; lockout and password rules then sit in Entra ID</t>
-        </is>
-      </c>
-      <c r="L5" s="12" t="inlineStr">
-        <is>
-          <t>Protocol and claims, MFA and conditional access, session life against the 30-minute inactivity rule, non-BDO users</t>
-        </is>
-      </c>
-      <c r="M5" s="12" t="inlineStr">
         <is>
           <t>IQ04</t>
         </is>
@@ -4338,30 +3871,10 @@
       </c>
       <c r="H6" s="12" t="inlineStr">
         <is>
-          <t>security, nbadmin (BRD-11 access requests)</t>
+          <t>Who owns requests and approvals, connector type, entitlement level, certification</t>
         </is>
       </c>
       <c r="I6" s="12" t="inlineStr">
-        <is>
-          <t>None for provisioning. nbadmin request lifecycle and UserAdminService apply changes; ExternalUserProvisioner serves portal users only</t>
-        </is>
-      </c>
-      <c r="J6" s="30" t="inlineStr">
-        <is>
-          <t>CHANGE</t>
-        </is>
-      </c>
-      <c r="K6" s="12" t="inlineStr">
-        <is>
-          <t>Provisioning API (SCIM 2.0 Users / Groups, or the connector ISC offers), aggregation export, change-log rows with the ISC request number; decide which BRD-11 request types remain in BIBS</t>
-        </is>
-      </c>
-      <c r="L6" s="12" t="inlineStr">
-        <is>
-          <t>Who owns requests and approvals, connector type, entitlement level, certification</t>
-        </is>
-      </c>
-      <c r="M6" s="12" t="inlineStr">
         <is>
           <t>IQ05</t>
         </is>
@@ -4405,30 +3918,10 @@
       </c>
       <c r="H7" s="12" t="inlineStr">
         <is>
-          <t>renewal (designed), submitted (designed), placement (CLPC reports), cashiering (PAY_CLPC)</t>
+          <t>Which LMS extracts, layouts, frequency, transport</t>
         </is>
       </c>
       <c r="I7" s="12" t="inlineStr">
-        <is>
-          <t>Bulk handlers RNW_LAMD_REPORT and SBM LAMD upload (designed); PaymentReportService / NB-CLPC-BILLING; PAY_CLPC</t>
-        </is>
-      </c>
-      <c r="J7" s="30" t="inlineStr">
-        <is>
-          <t>CHANGE</t>
-        </is>
-      </c>
-      <c r="K7" s="12" t="inlineStr">
-        <is>
-          <t>Layouts per report; automated transfer if LMS delivers files (SFTP drop to S3) instead of user uploads</t>
-        </is>
-      </c>
-      <c r="L7" s="12" t="inlineStr">
-        <is>
-          <t>Which LMS extracts, layouts, frequency, transport</t>
-        </is>
-      </c>
-      <c r="M7" s="12" t="inlineStr">
         <is>
           <t>IQ06</t>
         </is>
@@ -4472,30 +3965,10 @@
       </c>
       <c r="H8" s="12" t="inlineStr">
         <is>
-          <t>quotation, submitted (designed), placement (CLPC)</t>
+          <t>One interface or two, formats, frequency, transport</t>
         </is>
       </c>
       <c r="I8" s="12" t="inlineStr">
-        <is>
-          <t>quotation.service.QuotationRequestSource with job QUOTATION_REQUEST_INTAKE (cron off) and bulk QUOTATION_REQUEST; NB-CLPC-BILLING variants</t>
-        </is>
-      </c>
-      <c r="J8" s="30" t="inlineStr">
-        <is>
-          <t>CHANGE</t>
-        </is>
-      </c>
-      <c r="K8" s="12" t="inlineStr">
-        <is>
-          <t>QuotationRequestSource adapter (file or REST) with source authentication; SP intake handler; CLPC layout</t>
-        </is>
-      </c>
-      <c r="L8" s="12" t="inlineStr">
-        <is>
-          <t>One interface or two, formats, frequency, transport</t>
-        </is>
-      </c>
-      <c r="M8" s="12" t="inlineStr">
         <is>
           <t>IQ07</t>
         </is>
@@ -4539,30 +4012,10 @@
       </c>
       <c r="H9" s="12" t="inlineStr">
         <is>
-          <t>submitted (designed)</t>
+          <t>Drop, layout, transport</t>
         </is>
       </c>
       <c r="I9" s="12" t="inlineStr">
-        <is>
-          <t>Submitted-policy intake handlers (SUBMITTED_POLICIES_DESIGN); Q11 / SP-SQ01</t>
-        </is>
-      </c>
-      <c r="J9" s="30" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="K9" s="12" t="inlineStr">
-        <is>
-          <t>Intake layout and transfer; part of the SP build</t>
-        </is>
-      </c>
-      <c r="L9" s="12" t="inlineStr">
-        <is>
-          <t>Drop, layout, transport</t>
-        </is>
-      </c>
-      <c r="M9" s="12" t="inlineStr">
         <is>
           <t>IQ08</t>
         </is>
@@ -4606,30 +4059,10 @@
       </c>
       <c r="H10" s="12" t="inlineStr">
         <is>
-          <t>cashiering</t>
+          <t>Layout (OQ03), direction, frequency</t>
         </is>
       </c>
       <c r="I10" s="12" t="inlineStr">
-        <is>
-          <t>Payment file handler PAY_PDC (layout table, PdcFileHandler); job PDC_MATURITY</t>
-        </is>
-      </c>
-      <c r="J10" s="30" t="inlineStr">
-        <is>
-          <t>CONFIGURE</t>
-        </is>
-      </c>
-      <c r="K10" s="12" t="inlineStr">
-        <is>
-          <t>Layout in the payment-file layout table; an automated transfer if PMS drops files; outbound status feed if required</t>
-        </is>
-      </c>
-      <c r="L10" s="12" t="inlineStr">
-        <is>
-          <t>Layout (OQ03), direction, frequency</t>
-        </is>
-      </c>
-      <c r="M10" s="12" t="inlineStr">
         <is>
           <t>IQ09</t>
         </is>
@@ -4673,30 +4106,10 @@
       </c>
       <c r="H11" s="12" t="inlineStr">
         <is>
-          <t>disbursement</t>
+          <t>Layout, host-to-host or upload, cut-off times, approvals in CMS</t>
         </is>
       </c>
       <c r="I11" s="12" t="inlineStr">
-        <is>
-          <t>Payment instruments and EOD outputs (dsb_eod_output); DCTF file; upload DISB_BOB_APPROVED (BobApprovedHandler); BankChannelPort named in the design, not built (AQ09)</t>
-        </is>
-      </c>
-      <c r="J11" s="30" t="inlineStr">
-        <is>
-          <t>CHANGE</t>
-        </is>
-      </c>
-      <c r="K11" s="12" t="inlineStr">
-        <is>
-          <t>Outward payment file in the CMS layout (or host-to-host), status upload or pull, reconciliation to vouchers</t>
-        </is>
-      </c>
-      <c r="L11" s="12" t="inlineStr">
-        <is>
-          <t>Layout, host-to-host or upload, cut-off times, approvals in CMS</t>
-        </is>
-      </c>
-      <c r="M11" s="12" t="inlineStr">
         <is>
           <t>IQ10</t>
         </is>
@@ -4740,30 +4153,10 @@
       </c>
       <c r="H12" s="12" t="inlineStr">
         <is>
-          <t>cashiering</t>
+          <t>Layout, frequency, transport</t>
         </is>
       </c>
       <c r="I12" s="12" t="inlineStr">
-        <is>
-          <t>Payment file handler PAY_BILLS (configurable layout); PAYMENT_AUTOMATCH job</t>
-        </is>
-      </c>
-      <c r="J12" s="30" t="inlineStr">
-        <is>
-          <t>CONFIGURE</t>
-        </is>
-      </c>
-      <c r="K12" s="12" t="inlineStr">
-        <is>
-          <t>Layout; automated transfer if OBPCS drops files</t>
-        </is>
-      </c>
-      <c r="L12" s="12" t="inlineStr">
-        <is>
-          <t>Layout, frequency, transport</t>
-        </is>
-      </c>
-      <c r="M12" s="12" t="inlineStr">
         <is>
           <t>IQ10</t>
         </is>
@@ -4807,30 +4200,10 @@
       </c>
       <c r="H13" s="12" t="inlineStr">
         <is>
-          <t>cashiering (Direct Credit or a new layout)</t>
+          <t>Layout, SOA reference, frequency</t>
         </is>
       </c>
       <c r="I13" s="12" t="inlineStr">
-        <is>
-          <t>Payment file handler PAY_DIRECT_CREDIT or a new layout row</t>
-        </is>
-      </c>
-      <c r="J13" s="30" t="inlineStr">
-        <is>
-          <t>CONFIGURE</t>
-        </is>
-      </c>
-      <c r="K13" s="12" t="inlineStr">
-        <is>
-          <t>Layout; SOA-to-invoice matching rule if the file carries the SOA number only</t>
-        </is>
-      </c>
-      <c r="L13" s="12" t="inlineStr">
-        <is>
-          <t>Layout, SOA reference, frequency</t>
-        </is>
-      </c>
-      <c r="M13" s="12" t="inlineStr">
         <is>
           <t>IQ10</t>
         </is>
@@ -4874,30 +4247,10 @@
       </c>
       <c r="H14" s="12" t="inlineStr">
         <is>
-          <t>cashiering or disbursement</t>
+          <t>Purpose, direction, layout</t>
         </is>
       </c>
       <c r="I14" s="12" t="inlineStr">
-        <is>
-          <t>Payment file handlers; disbursement instruments</t>
-        </is>
-      </c>
-      <c r="J14" s="30" t="inlineStr">
-        <is>
-          <t>CHANGE</t>
-        </is>
-      </c>
-      <c r="K14" s="12" t="inlineStr">
-        <is>
-          <t>To size after the answer</t>
-        </is>
-      </c>
-      <c r="L14" s="12" t="inlineStr">
-        <is>
-          <t>Purpose, direction, layout</t>
-        </is>
-      </c>
-      <c r="M14" s="12" t="inlineStr">
         <is>
           <t>IQ10</t>
         </is>
@@ -4941,30 +4294,10 @@
       </c>
       <c r="H15" s="12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Confirm out of scope</t>
         </is>
       </c>
       <c r="I15" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J15" s="30" t="inlineStr">
-        <is>
-          <t>OUT</t>
-        </is>
-      </c>
-      <c r="K15" s="12" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L15" s="12" t="inlineStr">
-        <is>
-          <t>Confirm out of scope</t>
-        </is>
-      </c>
-      <c r="M15" s="12" t="inlineStr">
         <is>
           <t>IQ10</t>
         </is>
@@ -5008,30 +4341,10 @@
       </c>
       <c r="H16" s="12" t="inlineStr">
         <is>
-          <t>attachment; migration archive (designed)</t>
+          <t>Any ECM touch-point left</t>
         </is>
       </c>
       <c r="I16" s="12" t="inlineStr">
-        <is>
-          <t>migration ArchiveDocumentStore (designed)</t>
-        </is>
-      </c>
-      <c r="J16" s="30" t="inlineStr">
-        <is>
-          <t>OUT</t>
-        </is>
-      </c>
-      <c r="K16" s="12" t="inlineStr">
-        <is>
-          <t>None for document storage (S3); archive transfer if ECM holds legacy documents</t>
-        </is>
-      </c>
-      <c r="L16" s="12" t="inlineStr">
-        <is>
-          <t>Any ECM touch-point left</t>
-        </is>
-      </c>
-      <c r="M16" s="12" t="inlineStr">
         <is>
           <t>IQ13</t>
         </is>
@@ -5075,30 +4388,10 @@
       </c>
       <c r="H17" s="12" t="inlineStr">
         <is>
-          <t>messaging</t>
+          <t>SMTP or API, attachment limits, volume, bounce feedback, sender domains</t>
         </is>
       </c>
       <c r="I17" s="12" t="inlineStr">
-        <is>
-          <t>messaging.service.MailTransport (SmtpMailTransport, SimulatedMailTransport); outbox msg_outbound_message; MAIL_DISPATCH job; DocumentProtector</t>
-        </is>
-      </c>
-      <c r="J17" s="30" t="inlineStr">
-        <is>
-          <t>CONFIGURE</t>
-        </is>
-      </c>
-      <c r="K17" s="12" t="inlineStr">
-        <is>
-          <t>SMTP relay: configuration only. API: a new MailTransport adapter with status callback</t>
-        </is>
-      </c>
-      <c r="L17" s="12" t="inlineStr">
-        <is>
-          <t>SMTP or API, attachment limits, volume, bounce feedback, sender domains</t>
-        </is>
-      </c>
-      <c r="M17" s="12" t="inlineStr">
         <is>
           <t>IQ11</t>
         </is>
@@ -5127,7 +4420,7 @@
       </c>
       <c r="E18" s="12" t="inlineStr">
         <is>
-          <t>Mailboxes. Candidate uses are reading e-mailed quotation requests (BRNB.041, Q12 parked) and insurer replies, or relaying mail if CCM does not cover a case.</t>
+          <t>Mailboxes. Candidate uses are reading e-mailed quotation requests (BRNB.041, Q12 on hold) and insurer replies, or relaying mail if CCM does not cover a case.</t>
         </is>
       </c>
       <c r="F18" s="12" t="inlineStr">
@@ -5142,30 +4435,10 @@
       </c>
       <c r="H18" s="12" t="inlineStr">
         <is>
-          <t>quotation (request intake), messaging</t>
+          <t>Role against CCM, mailboxes, permissions</t>
         </is>
       </c>
       <c r="I18" s="12" t="inlineStr">
-        <is>
-          <t>None for mailbox reading (Q12); MailTransport for sending</t>
-        </is>
-      </c>
-      <c r="J18" s="30" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="K18" s="12" t="inlineStr">
-        <is>
-          <t>Mailbox reader through Microsoft Graph with an application registration, if confirmed</t>
-        </is>
-      </c>
-      <c r="L18" s="12" t="inlineStr">
-        <is>
-          <t>Role against CCM, mailboxes, permissions</t>
-        </is>
-      </c>
-      <c r="M18" s="12" t="inlineStr">
         <is>
           <t>IQ12</t>
         </is>
@@ -5209,30 +4482,10 @@
       </c>
       <c r="H19" s="12" t="inlineStr">
         <is>
-          <t>crm, cashiering</t>
+          <t>Which onboarding data, layout of the Trade file</t>
         </is>
       </c>
       <c r="I19" s="12" t="inlineStr">
-        <is>
-          <t>Client onboarding screens; payment file handler PAY_TRADE</t>
-        </is>
-      </c>
-      <c r="J19" s="30" t="inlineStr">
-        <is>
-          <t>FIT</t>
-        </is>
-      </c>
-      <c r="K19" s="12" t="inlineStr">
-        <is>
-          <t>None (layout confirmation only)</t>
-        </is>
-      </c>
-      <c r="L19" s="12" t="inlineStr">
-        <is>
-          <t>Which onboarding data, layout of the Trade file</t>
-        </is>
-      </c>
-      <c r="M19" s="12" t="inlineStr">
         <is>
           <t>IQ14</t>
         </is>
@@ -5276,30 +4529,10 @@
       </c>
       <c r="H20" s="12" t="inlineStr">
         <is>
-          <t>platform (events, report)</t>
+          <t>What SD 11 is, objects, format, frequency, push or pull</t>
         </is>
       </c>
       <c r="I20" s="12" t="inlineStr">
-        <is>
-          <t>Kafka integration events bibs.* (9 topics, PLATFORM_CACHE_AND_EVENTS.md); report exports; no bulk data feed</t>
-        </is>
-      </c>
-      <c r="J20" s="30" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="K20" s="12" t="inlineStr">
-        <is>
-          <t>Daily extracts to an S3 drop per the SD 11 specification, or change-data capture from a read replica; masking rules</t>
-        </is>
-      </c>
-      <c r="L20" s="12" t="inlineStr">
-        <is>
-          <t>What SD 11 is, objects, format, frequency, push or pull</t>
-        </is>
-      </c>
-      <c r="M20" s="12" t="inlineStr">
         <is>
           <t>IQ15</t>
         </is>
@@ -5343,30 +4576,10 @@
       </c>
       <c r="H21" s="12" t="inlineStr">
         <is>
-          <t>journal, ledger, coa, finreport</t>
+          <t>Level of detail, frequency, mapping, layout, transport</t>
         </is>
       </c>
       <c r="I21" s="12" t="inlineStr">
-        <is>
-          <t>None as an interface; GL reports (trial balance, GL-SCHEDULE); BDO GARD submission is report exports only (AQ31)</t>
-        </is>
-      </c>
-      <c r="J21" s="30" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="K21" s="12" t="inlineStr">
-        <is>
-          <t>EGL extract job with the account mapping (code map), control totals and reconciliation report</t>
-        </is>
-      </c>
-      <c r="L21" s="12" t="inlineStr">
-        <is>
-          <t>Level of detail, frequency, mapping, layout, transport</t>
-        </is>
-      </c>
-      <c r="M21" s="12" t="inlineStr">
         <is>
           <t>IQ16</t>
         </is>
@@ -5410,30 +4623,10 @@
       </c>
       <c r="H22" s="12" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>Purpose, data, direction</t>
         </is>
       </c>
       <c r="I22" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J22" s="30" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="K22" s="12" t="inlineStr">
-        <is>
-          <t>To size after the answer</t>
-        </is>
-      </c>
-      <c r="L22" s="12" t="inlineStr">
-        <is>
-          <t>Purpose, data, direction</t>
-        </is>
-      </c>
-      <c r="M22" s="12" t="inlineStr">
         <is>
           <t>IQ17</t>
         </is>
@@ -5477,30 +4670,10 @@
       </c>
       <c r="H23" s="12" t="inlineStr">
         <is>
-          <t>prodrecon, remittance, commission, renewal, acsl, issuance, brokerclaims</t>
+          <t>Insurers, processes, channel, layouts</t>
         </is>
       </c>
       <c r="I23" s="12" t="inlineStr">
-        <is>
-          <t>opsledger.service.port.InsurerFileInbox (default: no inbox, uploads on screens); FileDropPort for outgoing extracts</t>
-        </is>
-      </c>
-      <c r="J23" s="30" t="inlineStr">
-        <is>
-          <t>CHANGE</t>
-        </is>
-      </c>
-      <c r="K23" s="12" t="inlineStr">
-        <is>
-          <t>InsurerFileInbox adapter per channel (SFTP to S3, API) and outbound drops</t>
-        </is>
-      </c>
-      <c r="L23" s="12" t="inlineStr">
-        <is>
-          <t>Insurers, processes, channel, layouts</t>
-        </is>
-      </c>
-      <c r="M23" s="12" t="inlineStr">
         <is>
           <t>IQ18</t>
         </is>
@@ -5544,67 +4717,25 @@
       </c>
       <c r="H24" s="12" t="inlineStr">
         <is>
-          <t>screening</t>
+          <t>Does Bridger replace or complement BIBS list matching</t>
         </is>
       </c>
       <c r="I24" s="12" t="inlineStr">
         <is>
-          <t>Screening cases with evidence attachments; WatchlistFeed for list files (StagedFileWatchlistFeed)</t>
-        </is>
-      </c>
-      <c r="J24" s="30" t="inlineStr">
-        <is>
-          <t>CONFIGURE</t>
-        </is>
-      </c>
-      <c r="K24" s="12" t="inlineStr">
-        <is>
-          <t>Evidence document type and disposition values; a client export for Bridger batch screening if asked</t>
-        </is>
-      </c>
-      <c r="L24" s="12" t="inlineStr">
-        <is>
-          <t>Does Bridger replace or complement BIBS list matching</t>
-        </is>
-      </c>
-      <c r="M24" s="12" t="inlineStr">
-        <is>
           <t>IQ19</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:M24"/>
+  <autoFilter ref="A4:I24"/>
   <mergeCells count="1">
-    <mergeCell ref="A2:M2"/>
+    <mergeCell ref="A2:I2"/>
   </mergeCells>
-  <conditionalFormatting sqref="J5:J524">
-    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0" stopIfTrue="1">
-      <formula>"FIT"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="2" operator="equal" dxfId="1" stopIfTrue="1">
-      <formula>"CONFIGURE"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="3" operator="equal" dxfId="2" stopIfTrue="1">
-      <formula>"CHANGE"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="4" operator="equal" dxfId="3" stopIfTrue="1">
-      <formula>"NEW"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="5" operator="equal" dxfId="4" stopIfTrue="1">
-      <formula>"OUT"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A5:M524">
-    <cfRule type="expression" priority="6" dxfId="5">
+  <conditionalFormatting sqref="A5:I524">
+    <cfRule type="expression" priority="1" dxfId="0">
       <formula>AND(MOD(ROW(),2)=0,$A5&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="1">
-    <dataValidation sqref="J5:J524" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Fit" error="Choose a value from the list (Fit)." type="list">
-      <formula1>'_lists'!$A$1:$A$5</formula1>
-    </dataValidation>
-  </dataValidations>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
@@ -5625,52 +4756,45 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="38" customWidth="1" min="3" max="3"/>
-    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="24" t="inlineStr">
+      <c r="A1" s="19" t="inlineStr">
         <is>
           <t>Other interfaces</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="27" t="inlineStr">
+      <c r="A2" s="22" t="inlineStr">
         <is>
           <t>Interfaces named in the BRDs that the drop plan does not list</t>
         </is>
       </c>
     </row>
     <row r="3" ht="6" customHeight="1">
-      <c r="A3" s="28" t="n"/>
-      <c r="B3" s="28" t="n"/>
-      <c r="C3" s="28" t="n"/>
-      <c r="D3" s="28" t="n"/>
+      <c r="A3" s="23" t="n"/>
+      <c r="B3" s="23" t="n"/>
+      <c r="C3" s="23" t="n"/>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="29" t="inlineStr">
+      <c r="A4" s="24" t="inlineStr">
         <is>
           <t>Interface</t>
         </is>
       </c>
-      <c r="B4" s="29" t="inlineStr">
+      <c r="B4" s="24" t="inlineStr">
         <is>
           <t>Named in</t>
         </is>
       </c>
-      <c r="C4" s="29" t="inlineStr">
-        <is>
-          <t>BIBS seam</t>
-        </is>
-      </c>
-      <c r="D4" s="29" t="inlineStr">
+      <c r="C4" s="24" t="inlineStr">
         <is>
           <t>To confirm</t>
         </is>
@@ -5689,11 +4813,6 @@
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>RNW_LAMD_REPORT and SBM uploads (designed)</t>
-        </is>
-      </c>
-      <c r="D5" s="12" t="inlineStr">
-        <is>
           <t>Covered by LMS (INT-03)?</t>
         </is>
       </c>
@@ -5711,11 +4830,6 @@
       </c>
       <c r="C6" s="12" t="inlineStr">
         <is>
-          <t>PAY_CLPC, NB-CLPC-BILLING</t>
-        </is>
-      </c>
-      <c r="D6" s="12" t="inlineStr">
-        <is>
           <t>Covered by LMS / HL-LOAS?</t>
         </is>
       </c>
@@ -5733,11 +4847,6 @@
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>WatchlistFeed sources NLDS_PEP, AML_ADVISORY</t>
-        </is>
-      </c>
-      <c r="D7" s="12" t="inlineStr">
-        <is>
           <t>Transport (SQ01)</t>
         </is>
       </c>
@@ -5755,11 +4864,6 @@
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
-          <t>MailHouseGateway (designed)</t>
-        </is>
-      </c>
-      <c r="D8" s="12" t="inlineStr">
-        <is>
           <t>Channel and layout</t>
         </is>
       </c>
@@ -5777,11 +4881,6 @@
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>Export files per form</t>
-        </is>
-      </c>
-      <c r="D9" s="12" t="inlineStr">
-        <is>
           <t>Manual upload by Comptrollership</t>
         </is>
       </c>
@@ -5799,11 +4898,6 @@
       </c>
       <c r="C10" s="12" t="inlineStr">
         <is>
-          <t>Report exports</t>
-        </is>
-      </c>
-      <c r="D10" s="12" t="inlineStr">
-        <is>
           <t>AQ31; relation to EGL</t>
         </is>
       </c>
@@ -5821,22 +4915,17 @@
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>Migration intake (ExtractInbox, designed)</t>
-        </is>
-      </c>
-      <c r="D11" s="12" t="inlineStr">
-        <is>
           <t>Extract transport (DMQ28)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:D11"/>
+  <autoFilter ref="A4:C11"/>
   <mergeCells count="1">
-    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A2:C2"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:D511">
-    <cfRule type="expression" priority="1" dxfId="5">
+  <conditionalFormatting sqref="A5:C511">
+    <cfRule type="expression" priority="1" dxfId="0">
       <formula>AND(MOD(ROW(),2)=0,$A5&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5860,7 +4949,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J31"/>
+  <dimension ref="A1:H31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5869,85 +4958,71 @@
     <col width="26" customWidth="1" min="4" max="4"/>
     <col width="28" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="50" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="50" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="24" t="inlineStr">
+      <c r="A1" s="19" t="inlineStr">
         <is>
           <t>Drop map</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="27" t="inlineStr">
+      <c r="A2" s="22" t="inlineStr">
         <is>
           <t>Every line item of the drop plan mapped to BRDs, FRS and BIBS</t>
         </is>
       </c>
     </row>
     <row r="3" ht="6" customHeight="1">
-      <c r="A3" s="28" t="n"/>
-      <c r="B3" s="28" t="n"/>
-      <c r="C3" s="28" t="n"/>
-      <c r="D3" s="28" t="n"/>
-      <c r="E3" s="28" t="n"/>
-      <c r="F3" s="28" t="n"/>
-      <c r="G3" s="28" t="n"/>
-      <c r="H3" s="28" t="n"/>
-      <c r="I3" s="28" t="n"/>
-      <c r="J3" s="28" t="n"/>
+      <c r="A3" s="23" t="n"/>
+      <c r="B3" s="23" t="n"/>
+      <c r="C3" s="23" t="n"/>
+      <c r="D3" s="23" t="n"/>
+      <c r="E3" s="23" t="n"/>
+      <c r="F3" s="23" t="n"/>
+      <c r="G3" s="23" t="n"/>
+      <c r="H3" s="23" t="n"/>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="29" t="inlineStr">
+      <c r="A4" s="24" t="inlineStr">
         <is>
           <t>Drop</t>
         </is>
       </c>
-      <c r="B4" s="29" t="inlineStr">
+      <c r="B4" s="24" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="C4" s="29" t="inlineStr">
+      <c r="C4" s="24" t="inlineStr">
         <is>
           <t>Drop item</t>
         </is>
       </c>
-      <c r="D4" s="29" t="inlineStr">
+      <c r="D4" s="24" t="inlineStr">
         <is>
           <t>BRD named by BDOI</t>
         </is>
       </c>
-      <c r="E4" s="29" t="inlineStr">
+      <c r="E4" s="24" t="inlineStr">
         <is>
           <t>BIBS BRD</t>
         </is>
       </c>
-      <c r="F4" s="29" t="inlineStr">
+      <c r="F4" s="24" t="inlineStr">
         <is>
           <t>FRS</t>
         </is>
       </c>
-      <c r="G4" s="29" t="inlineStr">
-        <is>
-          <t>BIBS modules and screens</t>
-        </is>
-      </c>
-      <c r="H4" s="29" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="I4" s="29" t="inlineStr">
+      <c r="G4" s="24" t="inlineStr">
         <is>
           <t>Gap or mismatch</t>
         </is>
       </c>
-      <c r="J4" s="29" t="inlineStr">
+      <c r="H4" s="24" t="inlineStr">
         <is>
           <t>Refs</t>
         </is>
@@ -5986,20 +5061,10 @@
       </c>
       <c r="G5" s="12" t="inlineStr">
         <is>
-          <t>security (JWT log-in, lockout, sessions); Setup &amp; Administration &gt; Users; accessibility statement (deliverable 40)</t>
-        </is>
-      </c>
-      <c r="H5" s="30" t="inlineStr">
-        <is>
-          <t>Mixed</t>
-        </is>
-      </c>
-      <c r="I5" s="12" t="inlineStr">
-        <is>
-          <t>No BRD named. Log-in is built with local passwords; EIAM (Entra ID) sign-in is not built (the DirectoryAuthenticator port is for a password bind, not an OIDC redirect). "Accessibility" may mean WCAG (UAM-NFR-05) or system access.</t>
-        </is>
-      </c>
-      <c r="J5" s="12" t="inlineStr">
+          <t>No BRD named. Log-in uses BIBS passwords; EIAM (Entra ID) single sign-on is a Drop 0 integration (INT-01). "Accessibility" may mean WCAG (UAM-NFR-05) or system access.</t>
+        </is>
+      </c>
+      <c r="H5" s="12" t="inlineStr">
         <is>
           <t>IQ04, IQ24; DCR-214, DCR-230</t>
         </is>
@@ -6038,20 +5103,10 @@
       </c>
       <c r="G6" s="12" t="inlineStr">
         <is>
-          <t>security (roles, permissions, persona menus); Setup &amp; Administration &gt; Access Requests</t>
-        </is>
-      </c>
-      <c r="H6" s="30" t="inlineStr">
-        <is>
-          <t>Built</t>
-        </is>
-      </c>
-      <c r="I6" s="12" t="inlineStr">
-        <is>
           <t>No BRD named. Access requests and approvals are in BIBS (BRD-11); UIDM-ISC (the IGA) may take them over.</t>
         </is>
       </c>
-      <c r="J6" s="12" t="inlineStr">
+      <c r="H6" s="12" t="inlineStr">
         <is>
           <t>IQ05; DCR-229</t>
         </is>
@@ -6090,20 +5145,10 @@
       </c>
       <c r="G7" s="12" t="inlineStr">
         <is>
-          <t>nbadmin (request lifecycle, four eyes, bulk), security (UserAdminService, access change log)</t>
-        </is>
-      </c>
-      <c r="H7" s="30" t="inlineStr">
-        <is>
-          <t>Built</t>
-        </is>
-      </c>
-      <c r="I7" s="12" t="inlineStr">
-        <is>
           <t>Provisioning by UIDM-ISC conflicts with BRD-11 principle "a request in BIBS is the only way to change access".</t>
         </is>
       </c>
-      <c r="J7" s="12" t="inlineStr">
+      <c r="H7" s="12" t="inlineStr">
         <is>
           <t>IQ05; DCR-229</t>
         </is>
@@ -6142,20 +5187,10 @@
       </c>
       <c r="G8" s="12" t="inlineStr">
         <is>
-          <t>coa (chart, upload), lov (LOV master with approval), catalog (insurers), dimension; Broking Setup &gt; Lists of Values</t>
-        </is>
-      </c>
-      <c r="H8" s="30" t="inlineStr">
-        <is>
-          <t>Mixed</t>
-        </is>
-      </c>
-      <c r="I8" s="12" t="inlineStr">
-        <is>
-          <t>CORE-17 has no BRD: MIS field definition is NEW (CRQ09), insurer management is CHANGE (one screen). Acceptance criteria not stated.</t>
-        </is>
-      </c>
-      <c r="J8" s="12" t="inlineStr">
+          <t>CORE-17 has no BRD: MIS field definition (CRQ09) and insurer management (one screen) are proposed in FRS BRD-00. Acceptance criteria not stated.</t>
+        </is>
+      </c>
+      <c r="H8" s="12" t="inlineStr">
         <is>
           <t>IQ24; DCR-214</t>
         </is>
@@ -6194,20 +5229,10 @@
       </c>
       <c r="G9" s="12" t="inlineStr">
         <is>
-          <t>workflow (definitions, queues, SLA timers), approval (My Approvals)</t>
-        </is>
-      </c>
-      <c r="H9" s="30" t="inlineStr">
-        <is>
-          <t>Built</t>
-        </is>
-      </c>
-      <c r="I9" s="12" t="inlineStr">
-        <is>
-          <t>No BRD; accepted through the workflows of each BRD. The BRD-6, 8, 9, 12 and 13 workflows are designed, not built.</t>
-        </is>
-      </c>
-      <c r="J9" s="12" t="inlineStr">
+          <t>No BRD; accepted through the workflows of each BRD.</t>
+        </is>
+      </c>
+      <c r="H9" s="12" t="inlineStr">
         <is>
           <t>DCR-214</t>
         </is>
@@ -6246,20 +5271,10 @@
       </c>
       <c r="G10" s="12" t="inlineStr">
         <is>
-          <t>catalog, productmaint; Client &amp; Policy &gt; Products, Package Requests</t>
-        </is>
-      </c>
-      <c r="H10" s="30" t="inlineStr">
-        <is>
-          <t>Built</t>
-        </is>
-      </c>
-      <c r="I10" s="12" t="inlineStr">
-        <is>
           <t>None. BRD-3 is also named for Quotation (1.U2).</t>
         </is>
       </c>
-      <c r="J10" s="12" t="inlineStr">
+      <c r="H10" s="12" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -6298,20 +5313,10 @@
       </c>
       <c r="G11" s="12" t="inlineStr">
         <is>
-          <t>crm (Clients), screening (onboarding check); migration (designed)</t>
-        </is>
-      </c>
-      <c r="H11" s="30" t="inlineStr">
-        <is>
-          <t>Mixed</t>
-        </is>
-      </c>
-      <c r="I11" s="12" t="inlineStr">
-        <is>
-          <t>Client onboarding is built; client migration is designed. Screening at onboarding (BRD-10, built) is in no drop.</t>
-        </is>
-      </c>
-      <c r="J11" s="12" t="inlineStr">
+          <t>Client migration is part of BRD-13. Screening at onboarding (BRD-10) is in no drop.</t>
+        </is>
+      </c>
+      <c r="H11" s="12" t="inlineStr">
         <is>
           <t>IQ23; DCR-213</t>
         </is>
@@ -6350,20 +5355,10 @@
       </c>
       <c r="G12" s="12" t="inlineStr">
         <is>
-          <t>quotation, nonpackage; Client &amp; Policy &gt; Quotations, Proposal Requests</t>
-        </is>
-      </c>
-      <c r="H12" s="30" t="inlineStr">
-        <is>
-          <t>Built</t>
-        </is>
-      </c>
-      <c r="I12" s="12" t="inlineStr">
-        <is>
           <t>Non-Package Management (CORE-04) is not named; read as part of this item.</t>
         </is>
       </c>
-      <c r="J12" s="12" t="inlineStr">
+      <c r="H12" s="12" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -6402,20 +5397,10 @@
       </c>
       <c r="G13" s="12" t="inlineStr">
         <is>
-          <t>account (Accounts); csf (designed)</t>
-        </is>
-      </c>
-      <c r="H13" s="30" t="inlineStr">
-        <is>
-          <t>Mixed</t>
-        </is>
-      </c>
-      <c r="I13" s="12" t="inlineStr">
-        <is>
-          <t>Accounts are built; the CSF maintenance functions (contact updates, service requests) are designed, not built. The rest of CSF is in no drop.</t>
-        </is>
-      </c>
-      <c r="J13" s="12" t="inlineStr">
+          <t>Only the CSF maintenance functions (contact updates, service requests) are on the slide. The rest of CSF is in no drop.</t>
+        </is>
+      </c>
+      <c r="H13" s="12" t="inlineStr">
         <is>
           <t>IQ23; DCR-213</t>
         </is>
@@ -6454,20 +5439,10 @@
       </c>
       <c r="G14" s="12" t="inlineStr">
         <is>
-          <t>submitted (designed)</t>
-        </is>
-      </c>
-      <c r="H14" s="30" t="inlineStr">
-        <is>
-          <t>Designed</t>
-        </is>
-      </c>
-      <c r="I14" s="12" t="inlineStr">
-        <is>
-          <t>Build needed in wave 1 (Nov-Dec 2026). Sources LFS, HL-LOAS, LMS (LAMD) are integrations.</t>
-        </is>
-      </c>
-      <c r="J14" s="12" t="inlineStr">
+          <t>Sources LFS, HL-LOAS, LMS (LAMD) are integrations.</t>
+        </is>
+      </c>
+      <c r="H14" s="12" t="inlineStr">
         <is>
           <t>IQ06, IQ07, IQ08</t>
         </is>
@@ -6506,20 +5481,10 @@
       </c>
       <c r="G15" s="12" t="inlineStr">
         <is>
-          <t>renewal (designed; waves R0-R3)</t>
-        </is>
-      </c>
-      <c r="H15" s="30" t="inlineStr">
-        <is>
-          <t>Designed</t>
-        </is>
-      </c>
-      <c r="I15" s="12" t="inlineStr">
-        <is>
-          <t>Build needed in waves 1-2. The early renewal release is withdrawn (answer A1); legacy RMEL cohorts are carried forward at cut-over (P03).</t>
-        </is>
-      </c>
-      <c r="J15" s="12" t="inlineStr">
+          <t>The early renewal release is withdrawn (answer A1); legacy RMEL cohorts are carried forward at cut-over (P03).</t>
+        </is>
+      </c>
+      <c r="H15" s="12" t="inlineStr">
         <is>
           <t>IQ02, IQ03; DCR-218, DCR-219</t>
         </is>
@@ -6558,20 +5523,10 @@
       </c>
       <c r="G16" s="12" t="inlineStr">
         <is>
-          <t>placement, issuance (Placement and Issuance Workbenches); eb (designed)</t>
-        </is>
-      </c>
-      <c r="H16" s="30" t="inlineStr">
-        <is>
-          <t>Mixed</t>
-        </is>
-      </c>
-      <c r="I16" s="12" t="inlineStr">
-        <is>
           <t>EB placement is in Drop 1 while the EB module is in Drop 2.</t>
         </is>
       </c>
-      <c r="J16" s="12" t="inlineStr">
+      <c r="H16" s="12" t="inlineStr">
         <is>
           <t>IQ22; DCR-235</t>
         </is>
@@ -6610,20 +5565,10 @@
       </c>
       <c r="G17" s="12" t="inlineStr">
         <is>
-          <t>booking (Booking Workbench, EOD booking batch)</t>
-        </is>
-      </c>
-      <c r="H17" s="30" t="inlineStr">
-        <is>
-          <t>Mixed</t>
-        </is>
-      </c>
-      <c r="I17" s="12" t="inlineStr">
-        <is>
-          <t>Booking is built; the shared business-type change (V822, BT0) for renewal and submitted policies is designed.</t>
-        </is>
-      </c>
-      <c r="J17" s="12" t="inlineStr">
+          <t>Booking carries the business type (BT0) of renewal and submitted-policy accounts.</t>
+        </is>
+      </c>
+      <c r="H17" s="12" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -6662,20 +5607,10 @@
       </c>
       <c r="G18" s="12" t="inlineStr">
         <is>
-          <t>accounting engine (BROKER_BOOKING events), journal, ledger</t>
-        </is>
-      </c>
-      <c r="H18" s="30" t="inlineStr">
-        <is>
-          <t>Built</t>
-        </is>
-      </c>
-      <c r="I18" s="12" t="inlineStr">
-        <is>
           <t>Listed again as downstream 1.D5. Read as: upstream = postings of booking; downstream = GL, FRBS and ACSL.</t>
         </is>
       </c>
-      <c r="J18" s="12" t="inlineStr">
+      <c r="H18" s="12" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -6714,20 +5649,10 @@
       </c>
       <c r="G19" s="12" t="inlineStr">
         <is>
-          <t>nbreport, report (Report Centre); renewal, submitted, eb reports (designed)</t>
-        </is>
-      </c>
-      <c r="H19" s="30" t="inlineStr">
-        <is>
-          <t>Mixed</t>
-        </is>
-      </c>
-      <c r="I19" s="12" t="inlineStr">
-        <is>
-          <t>NB reports built; RN, SP and EB reports designed. The Report List is not split by drop.</t>
-        </is>
-      </c>
-      <c r="J19" s="12" t="inlineStr">
+          <t>The Report List is not split by drop.</t>
+        </is>
+      </c>
+      <c r="H19" s="12" t="inlineStr">
         <is>
           <t>DCR-235</t>
         </is>
@@ -6766,20 +5691,10 @@
       </c>
       <c r="G20" s="12" t="inlineStr">
         <is>
-          <t>disbursement, payrequest; Finance &gt; Disbursement Workbench</t>
-        </is>
-      </c>
-      <c r="H20" s="30" t="inlineStr">
-        <is>
-          <t>Built</t>
-        </is>
-      </c>
-      <c r="I20" s="12" t="inlineStr">
-        <is>
-          <t>Outward bank channel is CMS / New BOB (a file or host-to-host interface); today BOB approvals are uploaded (DISB_BOB_APPROVED).</t>
-        </is>
-      </c>
-      <c r="J20" s="12" t="inlineStr">
+          <t>Outward bank channel is CMS / New BOB (a file or host-to-host interface); until it is specified, BOB approvals are uploaded (DISB_BOB_APPROVED).</t>
+        </is>
+      </c>
+      <c r="H20" s="12" t="inlineStr">
         <is>
           <t>IQ10</t>
         </is>
@@ -6818,20 +5733,10 @@
       </c>
       <c r="G21" s="12" t="inlineStr">
         <is>
-          <t>cashiering (payment files PAY_BILLS, PAY_TRADE, PAY_CLPC, PAY_PDC, PAY_DIRECT_CREDIT; automatch; AR / OR)</t>
-        </is>
-      </c>
-      <c r="H21" s="30" t="inlineStr">
-        <is>
-          <t>Built</t>
-        </is>
-      </c>
-      <c r="I21" s="12" t="inlineStr">
-        <is>
           <t>The "Cashiering Addendum" is not in the BIBS pack. Channels OBPCS, Old BOB, PMS and TFS feed this module.</t>
         </is>
       </c>
-      <c r="J21" s="12" t="inlineStr">
+      <c r="H21" s="12" t="inlineStr">
         <is>
           <t>IQ09, IQ10, IQ14, IQ20; DCR-215</t>
         </is>
@@ -6870,20 +5775,10 @@
       </c>
       <c r="G22" s="12" t="inlineStr">
         <is>
-          <t>remittance (extraction, batches, holds, special remittances)</t>
-        </is>
-      </c>
-      <c r="H22" s="30" t="inlineStr">
-        <is>
-          <t>Built</t>
-        </is>
-      </c>
-      <c r="I22" s="12" t="inlineStr">
-        <is>
           <t>Answer A3: Remittance handles the reinsurance transactions in Drop 1; the reinsurance module is phase 2. Which RI transactions, and the "Remittance Addendum", are not defined.</t>
         </is>
       </c>
-      <c r="J22" s="12" t="inlineStr">
+      <c r="H22" s="12" t="inlineStr">
         <is>
           <t>IQ20; DCR-210, DCR-215</t>
         </is>
@@ -6922,20 +5817,10 @@
       </c>
       <c r="G23" s="12" t="inlineStr">
         <is>
-          <t>adjustment (Adjustment Workbench)</t>
-        </is>
-      </c>
-      <c r="H23" s="30" t="inlineStr">
-        <is>
-          <t>Built</t>
-        </is>
-      </c>
-      <c r="I23" s="12" t="inlineStr">
-        <is>
           <t>None.</t>
         </is>
       </c>
-      <c r="J23" s="12" t="inlineStr">
+      <c r="H23" s="12" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -6974,20 +5859,10 @@
       </c>
       <c r="G24" s="12" t="inlineStr">
         <is>
-          <t>coa, journal, ledger, period, closing, frbs, acsl</t>
-        </is>
-      </c>
-      <c r="H24" s="30" t="inlineStr">
-        <is>
-          <t>Built</t>
-        </is>
-      </c>
-      <c r="I24" s="12" t="inlineStr">
-        <is>
-          <t>EGL (Drop 2 integration) takes GL data out of BIBS; not built.</t>
-        </is>
-      </c>
-      <c r="J24" s="12" t="inlineStr">
+          <t>EGL (Drop 2 integration, INT-17) takes GL data out of BIBS.</t>
+        </is>
+      </c>
+      <c r="H24" s="12" t="inlineStr">
         <is>
           <t>IQ16</t>
         </is>
@@ -7026,20 +5901,10 @@
       </c>
       <c r="G25" s="12" t="inlineStr">
         <is>
-          <t>tax (BIR forms, 2307, alphalists), finreport, frbs report pack</t>
-        </is>
-      </c>
-      <c r="H25" s="30" t="inlineStr">
-        <is>
-          <t>Built</t>
-        </is>
-      </c>
-      <c r="I25" s="12" t="inlineStr">
-        <is>
           <t>Legacy-period figures in BIR reports depend on the migration of open items and the GL opening (DMQ18).</t>
         </is>
       </c>
-      <c r="J25" s="12" t="inlineStr">
+      <c r="H25" s="12" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -7078,20 +5943,10 @@
       </c>
       <c r="G26" s="12" t="inlineStr">
         <is>
-          <t>commission (DP billing), collections (DP PR lists)</t>
-        </is>
-      </c>
-      <c r="H26" s="30" t="inlineStr">
-        <is>
-          <t>Built</t>
-        </is>
-      </c>
-      <c r="I26" s="12" t="inlineStr">
-        <is>
           <t>BRCLXN.061-064 are in the unsigned draft addendum only (CQ01).</t>
         </is>
       </c>
-      <c r="J26" s="12" t="inlineStr">
+      <c r="H26" s="12" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -7130,20 +5985,10 @@
       </c>
       <c r="G27" s="12" t="inlineStr">
         <is>
-          <t>collections (worklists, dispositions, daily files), opsledger CollectionFeed</t>
-        </is>
-      </c>
-      <c r="H27" s="30" t="inlineStr">
-        <is>
-          <t>Built</t>
-        </is>
-      </c>
-      <c r="I27" s="12" t="inlineStr">
-        <is>
           <t>BRD-4 is a BIBS module fed by the Operations ledger; "extraction" is undefined (a feed to a separate CMS application, or the daily files?).</t>
         </is>
       </c>
-      <c r="J27" s="12" t="inlineStr">
+      <c r="H27" s="12" t="inlineStr">
         <is>
           <t>IQ21; DCR-212, DCR-221</t>
         </is>
@@ -7182,20 +6027,10 @@
       </c>
       <c r="G28" s="12" t="inlineStr">
         <is>
-          <t>brokerclaims (Claims Home)</t>
-        </is>
-      </c>
-      <c r="H28" s="30" t="inlineStr">
-        <is>
-          <t>Being built</t>
-        </is>
-      </c>
-      <c r="I28" s="12" t="inlineStr">
-        <is>
-          <t>Built ahead of the drop; open-claims migration (F07) is conditional (CLQ14).</t>
-        </is>
-      </c>
-      <c r="J28" s="12" t="inlineStr">
+          <t>Open-claims migration (F07) is conditional (CLQ14).</t>
+        </is>
+      </c>
+      <c r="H28" s="12" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -7234,20 +6069,10 @@
       </c>
       <c r="G29" s="12" t="inlineStr">
         <is>
-          <t>prodrecon (Reconciliation Workbench)</t>
-        </is>
-      </c>
-      <c r="H29" s="30" t="inlineStr">
-        <is>
-          <t>Built</t>
-        </is>
-      </c>
-      <c r="I29" s="12" t="inlineStr">
-        <is>
-          <t>Built with Operations; tested in SIT Drop 2 as BDOI plans. Insurer feedback files are an Insurer System integration.</t>
-        </is>
-      </c>
-      <c r="J29" s="12" t="inlineStr">
+          <t>Specified in the Operations FRS; tested in SIT Drop 2 as BDOI plans. Insurer feedback files are an Insurer System integration.</t>
+        </is>
+      </c>
+      <c r="H29" s="12" t="inlineStr">
         <is>
           <t>IQ18</t>
         </is>
@@ -7286,20 +6111,10 @@
       </c>
       <c r="G30" s="12" t="inlineStr">
         <is>
-          <t>eb (designed); portal module (designed) to be dropped</t>
-        </is>
-      </c>
-      <c r="H30" s="30" t="inlineStr">
-        <is>
-          <t>Designed</t>
-        </is>
-      </c>
-      <c r="I30" s="12" t="inlineStr">
-        <is>
-          <t>BRD-8 BRID-005, 005.01, 014 and the EB design use an insurer / client-HR portal; the IER diagram shows an "EB Insurer Portal" tenant.</t>
-        </is>
-      </c>
-      <c r="J30" s="12" t="inlineStr">
+          <t>BRD-8 BRID-005, 005.01, 014 and FRS BRD-8 use an insurer / client-HR portal; the IER diagram shows an "EB Insurer Portal" tenant.</t>
+        </is>
+      </c>
+      <c r="H30" s="12" t="inlineStr">
         <is>
           <t>IQ22; DCR-211</t>
         </is>
@@ -7338,97 +6153,22 @@
       </c>
       <c r="G31" s="12" t="inlineStr">
         <is>
-          <t>report (Report Centre, 174 definitions)</t>
-        </is>
-      </c>
-      <c r="H31" s="30" t="inlineStr">
-        <is>
-          <t>Mixed</t>
-        </is>
-      </c>
-      <c r="I31" s="12" t="inlineStr">
-        <is>
           <t>"Other" is not defined; propose: every Report List item not owned by a Drop 1 module.</t>
         </is>
       </c>
-      <c r="J31" s="12" t="inlineStr">
+      <c r="H31" s="12" t="inlineStr">
         <is>
           <t>DCR-235</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:J31"/>
+  <autoFilter ref="A4:H31"/>
   <mergeCells count="1">
-    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A2:H2"/>
   </mergeCells>
-  <conditionalFormatting sqref="H5:H531">
-    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0" stopIfTrue="1">
-      <formula>"FIT"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="2" operator="equal" dxfId="0" stopIfTrue="1">
-      <formula>"PASS"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="3" operator="equal" dxfId="0" stopIfTrue="1">
-      <formula>"PASSED"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="4" operator="equal" dxfId="0" stopIfTrue="1">
-      <formula>"DONE"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="5" operator="equal" dxfId="0" stopIfTrue="1">
-      <formula>"CLOSED"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="6" operator="equal" dxfId="0" stopIfTrue="1">
-      <formula>"ANSWERED"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="7" operator="equal" dxfId="0" stopIfTrue="1">
-      <formula>"BUILT"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="8" operator="equal" dxfId="1" stopIfTrue="1">
-      <formula>"CONFIGURE"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="9" operator="equal" dxfId="1" stopIfTrue="1">
-      <formula>"RECOMMENDED"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="10" operator="equal" dxfId="2" stopIfTrue="1">
-      <formula>"CHANGE"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="11" operator="equal" dxfId="2" stopIfTrue="1">
-      <formula>"PARTIAL"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="12" operator="equal" dxfId="2" stopIfTrue="1">
-      <formula>"IN PROGRESS"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="13" operator="equal" dxfId="2" stopIfTrue="1">
-      <formula>"OPEN"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="14" operator="equal" dxfId="3" stopIfTrue="1">
-      <formula>"NEW"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="15" operator="equal" dxfId="6" stopIfTrue="1">
-      <formula>"GAP"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="16" operator="equal" dxfId="6" stopIfTrue="1">
-      <formula>"FAIL"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="17" operator="equal" dxfId="6" stopIfTrue="1">
-      <formula>"FAILED"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="18" operator="equal" dxfId="6" stopIfTrue="1">
-      <formula>"BLOCKED"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="19" operator="equal" dxfId="4" stopIfTrue="1">
-      <formula>"OUT"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="20" operator="equal" dxfId="4" stopIfTrue="1">
-      <formula>"PARKED"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="21" operator="equal" dxfId="4" stopIfTrue="1">
-      <formula>"N/A"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A5:J531">
-    <cfRule type="expression" priority="22" dxfId="5">
+  <conditionalFormatting sqref="A5:H531">
+    <cfRule type="expression" priority="1" dxfId="0">
       <formula>AND(MOD(ROW(),2)=0,$A5&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7464,54 +6204,54 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="24" t="inlineStr">
+      <c r="A1" s="19" t="inlineStr">
         <is>
           <t>Documents by drop</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="27" t="inlineStr">
+      <c r="A2" s="22" t="inlineStr">
         <is>
           <t>Drop-to-document map for the folder restructure (answer A5)</t>
         </is>
       </c>
     </row>
     <row r="3" ht="6" customHeight="1">
-      <c r="A3" s="28" t="n"/>
-      <c r="B3" s="28" t="n"/>
-      <c r="C3" s="28" t="n"/>
-      <c r="D3" s="28" t="n"/>
-      <c r="E3" s="28" t="n"/>
-      <c r="F3" s="28" t="n"/>
+      <c r="A3" s="23" t="n"/>
+      <c r="B3" s="23" t="n"/>
+      <c r="C3" s="23" t="n"/>
+      <c r="D3" s="23" t="n"/>
+      <c r="E3" s="23" t="n"/>
+      <c r="F3" s="23" t="n"/>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="29" t="inlineStr">
+      <c r="A4" s="24" t="inlineStr">
         <is>
           <t>Document</t>
         </is>
       </c>
-      <c r="B4" s="29" t="inlineStr">
+      <c r="B4" s="24" t="inlineStr">
         <is>
           <t>Kind</t>
         </is>
       </c>
-      <c r="C4" s="29" t="inlineStr">
+      <c r="C4" s="24" t="inlineStr">
         <is>
           <t>File</t>
         </is>
       </c>
-      <c r="D4" s="29" t="inlineStr">
+      <c r="D4" s="24" t="inlineStr">
         <is>
           <t>Drop (folder)</t>
         </is>
       </c>
-      <c r="E4" s="29" t="inlineStr">
+      <c r="E4" s="24" t="inlineStr">
         <is>
           <t>Shared with</t>
         </is>
       </c>
-      <c r="F4" s="29" t="inlineStr">
+      <c r="F4" s="24" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
@@ -7626,7 +6366,7 @@
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
-          <t>BIBS_FRS_BRD-13_*; BIBS_TestPlan_BRD-13_*; out/Drop-0_Setup_and_Data_Migration/Migration/*</t>
+          <t>BIBS_FRS_BRD-13_*; BIBS_TestPlan_BRD-13_*; BIBS_Migration_BRD-13_* and the extract templates</t>
         </is>
       </c>
       <c r="D8" s="12" t="inlineStr">
@@ -7978,7 +6718,7 @@
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>BDOI_REPORT_LIST.md</t>
+          <t>Report List (BDOI)</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
@@ -8121,7 +6861,7 @@
       </c>
       <c r="F23" s="12" t="inlineStr">
         <is>
-          <t>Built from section 6 and the IER</t>
+          <t>From section 6 and the IER</t>
         </is>
       </c>
     </row>
@@ -8259,7 +6999,7 @@
     <mergeCell ref="A2:F2"/>
   </mergeCells>
   <conditionalFormatting sqref="A5:F527">
-    <cfRule type="expression" priority="1" dxfId="5">
+    <cfRule type="expression" priority="1" dxfId="0">
       <formula>AND(MOD(ROW(),2)=0,$A5&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8295,54 +7035,54 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="24" t="inlineStr">
+      <c r="A1" s="19" t="inlineStr">
         <is>
           <t>Infrastructure</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="27" t="inlineStr">
+      <c r="A2" s="22" t="inlineStr">
         <is>
           <t>IER workbook v20 against the BIBS architecture and deployment</t>
         </is>
       </c>
     </row>
     <row r="3" ht="6" customHeight="1">
-      <c r="A3" s="28" t="n"/>
-      <c r="B3" s="28" t="n"/>
-      <c r="C3" s="28" t="n"/>
-      <c r="D3" s="28" t="n"/>
-      <c r="E3" s="28" t="n"/>
-      <c r="F3" s="28" t="n"/>
+      <c r="A3" s="23" t="n"/>
+      <c r="B3" s="23" t="n"/>
+      <c r="C3" s="23" t="n"/>
+      <c r="D3" s="23" t="n"/>
+      <c r="E3" s="23" t="n"/>
+      <c r="F3" s="23" t="n"/>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="29" t="inlineStr">
+      <c r="A4" s="24" t="inlineStr">
         <is>
           <t>Topic</t>
         </is>
       </c>
-      <c r="B4" s="29" t="inlineStr">
+      <c r="B4" s="24" t="inlineStr">
         <is>
           <t>IER (BDOI IT)</t>
         </is>
       </c>
-      <c r="C4" s="29" t="inlineStr">
-        <is>
-          <t>BIBS as built</t>
-        </is>
-      </c>
-      <c r="D4" s="29" t="inlineStr">
+      <c r="C4" s="24" t="inlineStr">
+        <is>
+          <t>BIBS</t>
+        </is>
+      </c>
+      <c r="D4" s="24" t="inlineStr">
         <is>
           <t>Assessment</t>
         </is>
       </c>
-      <c r="E4" s="29" t="inlineStr">
+      <c r="E4" s="24" t="inlineStr">
         <is>
           <t>Change needed</t>
         </is>
       </c>
-      <c r="F4" s="29" t="inlineStr">
+      <c r="F4" s="24" t="inlineStr">
         <is>
           <t>Ref</t>
         </is>
@@ -8361,10 +7101,10 @@
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>One Spring Boot 3.5 modular monolith (backend) and one React SPA served by nginx (frontend); modules isolated by ArchUnit; a business record, its journal, ledger and sub-ledger rows commit in one PostgreSQL transaction</t>
-        </is>
-      </c>
-      <c r="D5" s="30" t="inlineStr">
+          <t>One Spring Boot 3.5 modular monolith (backend) and one React SPA served by nginx (frontend); a business record, its journal, ledger and sub-ledger rows commit in one PostgreSQL transaction</t>
+        </is>
+      </c>
+      <c r="D5" s="25" t="inlineStr">
         <is>
           <t>Mismatch</t>
         </is>
@@ -8388,15 +7128,15 @@
       </c>
       <c r="B6" s="12" t="inlineStr">
         <is>
-          <t>Three tenants: BDOI internal ~1,200 users, EB insurer portal ~50 partners, broker / RI network ~200 accounts; tenant_id + RLS per data layer</t>
+          <t>Three tenants: BDOI internal ~1,200 users, EB insurer portal ~50 partners, broker / RI network ~200 accounts; a tenant key and row-level security per data layer</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
         <is>
-          <t>Single tenant (company_id, branch scope, role scope); no portal (EB portal dropped by answer); RI network is phase 2</t>
-        </is>
-      </c>
-      <c r="D6" s="30" t="inlineStr">
+          <t>Single tenant (company, branch scope, role scope); no portal (EB portal dropped by answer); RI network is phase 2</t>
+        </is>
+      </c>
+      <c r="D6" s="25" t="inlineStr">
         <is>
           <t>Mismatch</t>
         </is>
@@ -8425,10 +7165,10 @@
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>Two deployments: brokerverse-backend (2 replicas, 500m / 1 Gi requests, 2 CPU / 2 Gi limits) and brokerverse-frontend (2 replicas); namespace brokerverse (deploy/k8s/brokerverse.yaml)</t>
-        </is>
-      </c>
-      <c r="D7" s="30" t="inlineStr">
+          <t>Two deployments: brokerverse-backend (2 replicas, 500m / 1 Gi requests, 2 CPU / 2 Gi limits) and brokerverse-frontend (2 replicas); one namespace</t>
+        </is>
+      </c>
+      <c r="D7" s="25" t="inlineStr">
         <is>
           <t>Mismatch</t>
         </is>
@@ -8457,10 +7197,10 @@
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
-          <t>PostgreSQL 16 with Flyway, JSONB where needed; Amazon RDS Multi-AZ in production (deploy notes); no MongoDB</t>
-        </is>
-      </c>
-      <c r="D8" s="30" t="inlineStr">
+          <t>PostgreSQL 16 with versioned schema scripts, JSONB where needed; Amazon RDS Multi-AZ in production (deploy notes); no MongoDB</t>
+        </is>
+      </c>
+      <c r="D8" s="25" t="inlineStr">
         <is>
           <t>Aligned (RDS); Mismatch (Aurora, Mongo, "RHEL 9")</t>
         </is>
@@ -8492,14 +7232,14 @@
           <t>Redis 7 with cluster mode disabled (one shard, primary + replica, TLS, AUTH); the cache clear uses SCAN and the job lock uses scripts on single keys</t>
         </is>
       </c>
-      <c r="D9" s="30" t="inlineStr">
+      <c r="D9" s="25" t="inlineStr">
         <is>
           <t>Mismatch (wording)</t>
         </is>
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>IER: cluster mode disabled, Multi-AZ replica. Code change only if cluster mode enabled is imposed</t>
+          <t>IER: cluster mode disabled, Multi-AZ replica. A change in BIBS only if cluster mode enabled is imposed</t>
         </is>
       </c>
       <c r="F9" s="12" t="inlineStr">
@@ -8521,17 +7261,17 @@
       </c>
       <c r="C10" s="12" t="inlineStr">
         <is>
-          <t>MSK Kafka 3.6+ with SASL/SCRAM + TLS, 9 topics bibs.* plus .dlt, transactional outbox; no EventBridge, no schema registry</t>
-        </is>
-      </c>
-      <c r="D10" s="30" t="inlineStr">
+          <t>MSK Kafka 3.6+ with SASL/SCRAM + TLS, 9 topics plus dead-letter topics, transactional outbox; no EventBridge, no schema registry</t>
+        </is>
+      </c>
+      <c r="D10" s="25" t="inlineStr">
         <is>
           <t>Aligned (MSK); Mismatch (EventBridge, 80 topics)</t>
         </is>
       </c>
       <c r="E10" s="12" t="inlineStr">
         <is>
-          <t>IER: 3 brokers kafka.m5.large class, 9 topics x 3 partitions; DEV / SIT with 2 brokers need BROKERVERSE_KAFKA_REPLICATION_FACTOR=2</t>
+          <t>IER: 3 brokers kafka.m5.large class, 9 topics x 3 partitions; DEV / SIT with 2 brokers need a replication factor of 2</t>
         </is>
       </c>
       <c r="F10" s="12" t="inlineStr">
@@ -8553,17 +7293,17 @@
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>File content in PostgreSQL bytea in 13 tables (doc_attachment_content and others); no volume on the pods</t>
-        </is>
-      </c>
-      <c r="D11" s="30" t="inlineStr">
+          <t>File content in PostgreSQL; no volume on the pods</t>
+        </is>
+      </c>
+      <c r="D11" s="25" t="inlineStr">
         <is>
           <t>Mismatch</t>
         </is>
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
-          <t>Answer A4 and DOCUMENT_STORAGE_DECISION.md (option C, steps ST0 / ST1): S3 for bytes, PostgreSQL for metadata; no EFS for BIBS. The EFS totals are a formula error (Total PV = max replicas x CPU limit)</t>
+          <t>Answer A4 and the document storage decision (option C): S3 for the file content, PostgreSQL for metadata; no EFS for BIBS. The EFS totals are a formula error (Total PV = max replicas x CPU limit)</t>
         </is>
       </c>
       <c r="F11" s="12" t="inlineStr">
@@ -8585,10 +7325,10 @@
       </c>
       <c r="C12" s="12" t="inlineStr">
         <is>
-          <t>Kubernetes Ingress to the nginx frontend, /api proxied to the backend; JWT issued by BIBS; login rate limit in the application</t>
-        </is>
-      </c>
-      <c r="D12" s="30" t="inlineStr">
+          <t>Kubernetes Ingress to the nginx frontend, API calls proxied to the backend; JWT issued by BIBS; login rate limit in the application</t>
+        </is>
+      </c>
+      <c r="D12" s="25" t="inlineStr">
         <is>
           <t>Gap</t>
         </is>
@@ -8612,7 +7352,7 @@
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>VDI: OpenJDK Temurin 17 ("BrokerVerse services build on JDK 17"), Node 20, Angular SPA</t>
+          <t>VDI: OpenJDK Temurin 17 for the BrokerVerse services, Node 20, Angular SPA</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
@@ -8620,7 +7360,7 @@
           <t>Java 21 (Temurin 21 JRE Alpine image), Spring Boot 3.5, Node 22, React 19, Vite 8</t>
         </is>
       </c>
-      <c r="D13" s="30" t="inlineStr">
+      <c r="D13" s="25" t="inlineStr">
         <is>
           <t>Mismatch</t>
         </is>
@@ -8649,10 +7389,10 @@
       </c>
       <c r="C14" s="12" t="inlineStr">
         <is>
-          <t>the CI pipeline (.gitlab-ci.yml: mvn verify, SonarQube, npm verify); plain Kubernetes manifests; no Helm chart</t>
-        </is>
-      </c>
-      <c r="D14" s="30" t="inlineStr">
+          <t>One delivery pipeline with SonarQube analysis; plain Kubernetes manifests; no Helm chart</t>
+        </is>
+      </c>
+      <c r="D14" s="25" t="inlineStr">
         <is>
           <t>Gap</t>
         </is>
@@ -8681,10 +7421,10 @@
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>Actuator health, metrics and /actuator/prometheus; structured logs with CR/LF neutralised; alert catalogue planned (deliverable 38)</t>
-        </is>
-      </c>
-      <c r="D15" s="30" t="inlineStr">
+          <t>Health checks and Prometheus metrics; structured logs with CR/LF neutralised; alert catalogue planned (deliverable 38)</t>
+        </is>
+      </c>
+      <c r="D15" s="25" t="inlineStr">
         <is>
           <t>Gap</t>
         </is>
@@ -8716,7 +7456,7 @@
           <t>Register proposal DCR-135: RPO 15 min (continuous WAL archiving), RTO 4 h; RUNBOOK: daily full backup + WAL archiving, quarterly restore test</t>
         </is>
       </c>
-      <c r="D16" s="30" t="inlineStr">
+      <c r="D16" s="25" t="inlineStr">
         <is>
           <t>Aligned</t>
         </is>
@@ -8748,14 +7488,14 @@
           <t>Hosting appendix: AWS ap-southeast-1; access restricted to personnel in the Philippines</t>
         </is>
       </c>
-      <c r="D17" s="30" t="inlineStr">
+      <c r="D17" s="25" t="inlineStr">
         <is>
           <t>Gap</t>
         </is>
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>Name the DR region and confirm data residency; S3 cross-region replication and MSK / ElastiCache rebuild in DR; DR runbook</t>
+          <t>Name the DR region and confirm data residency; S3 cross-region replication and MSK / ElastiCache re-created in DR; DR runbook</t>
         </is>
       </c>
       <c r="F17" s="12" t="inlineStr">
@@ -8780,7 +7520,7 @@
           <t>Needs all six; Pre-Prod for the dress rehearsal and performance tests; DR for the failover test</t>
         </is>
       </c>
-      <c r="D18" s="30" t="inlineStr">
+      <c r="D18" s="25" t="inlineStr">
         <is>
           <t>Gap</t>
         </is>
@@ -8812,7 +7552,7 @@
           <t>Night jobs in PHT: EOD booking and remittance extraction 20:00, Collections 22:15-23:00, renewal extraction 01:00, screening 01:00-01:30, application file 05:00, alerts 06:00</t>
         </is>
       </c>
-      <c r="D19" s="30" t="inlineStr">
+      <c r="D19" s="25" t="inlineStr">
         <is>
           <t>Mismatch</t>
         </is>
@@ -8844,7 +7584,7 @@
           <t>Umbrella BRD p.42: 1,344 named / 429 concurrent (DCR-166); renewal 25,800 accounts and NB 21,200 bookings a month</t>
         </is>
       </c>
-      <c r="D20" s="30" t="inlineStr">
+      <c r="D20" s="25" t="inlineStr">
         <is>
           <t>Gap</t>
         </is>
@@ -8876,7 +7616,7 @@
           <t>Hosting appendix: access restricted to personnel in the Philippines; migration staging purged within 5 days</t>
         </is>
       </c>
-      <c r="D21" s="30" t="inlineStr">
+      <c r="D21" s="25" t="inlineStr">
         <is>
           <t>Gap</t>
         </is>
@@ -8898,72 +7638,75 @@
     <mergeCell ref="A2:F2"/>
   </mergeCells>
   <conditionalFormatting sqref="D5:D521">
-    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0" stopIfTrue="1">
+    <cfRule type="cellIs" priority="1" operator="equal" dxfId="1" stopIfTrue="1">
       <formula>"FIT"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="2" operator="equal" dxfId="0" stopIfTrue="1">
+    <cfRule type="cellIs" priority="2" operator="equal" dxfId="1" stopIfTrue="1">
       <formula>"PASS"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="3" operator="equal" dxfId="0" stopIfTrue="1">
+    <cfRule type="cellIs" priority="3" operator="equal" dxfId="1" stopIfTrue="1">
       <formula>"PASSED"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="4" operator="equal" dxfId="0" stopIfTrue="1">
+    <cfRule type="cellIs" priority="4" operator="equal" dxfId="1" stopIfTrue="1">
       <formula>"DONE"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="5" operator="equal" dxfId="0" stopIfTrue="1">
+    <cfRule type="cellIs" priority="5" operator="equal" dxfId="1" stopIfTrue="1">
       <formula>"CLOSED"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="6" operator="equal" dxfId="0" stopIfTrue="1">
+    <cfRule type="cellIs" priority="6" operator="equal" dxfId="1" stopIfTrue="1">
       <formula>"ANSWERED"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="7" operator="equal" dxfId="0" stopIfTrue="1">
-      <formula>"BUILT"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="8" operator="equal" dxfId="1" stopIfTrue="1">
+    <cfRule type="cellIs" priority="7" operator="equal" dxfId="2" stopIfTrue="1">
       <formula>"CONFIGURE"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="9" operator="equal" dxfId="1" stopIfTrue="1">
+    <cfRule type="cellIs" priority="8" operator="equal" dxfId="2" stopIfTrue="1">
       <formula>"RECOMMENDED"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="10" operator="equal" dxfId="2" stopIfTrue="1">
+    <cfRule type="cellIs" priority="9" operator="equal" dxfId="2" stopIfTrue="1">
+      <formula>"IN SCOPE"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="10" operator="equal" dxfId="3" stopIfTrue="1">
       <formula>"CHANGE"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="11" operator="equal" dxfId="2" stopIfTrue="1">
+    <cfRule type="cellIs" priority="11" operator="equal" dxfId="3" stopIfTrue="1">
       <formula>"PARTIAL"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="12" operator="equal" dxfId="2" stopIfTrue="1">
+    <cfRule type="cellIs" priority="12" operator="equal" dxfId="3" stopIfTrue="1">
       <formula>"IN PROGRESS"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="13" operator="equal" dxfId="2" stopIfTrue="1">
+    <cfRule type="cellIs" priority="13" operator="equal" dxfId="3" stopIfTrue="1">
       <formula>"OPEN"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="14" operator="equal" dxfId="3" stopIfTrue="1">
+    <cfRule type="cellIs" priority="14" operator="equal" dxfId="4" stopIfTrue="1">
       <formula>"NEW"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="15" operator="equal" dxfId="6" stopIfTrue="1">
+    <cfRule type="cellIs" priority="15" operator="equal" dxfId="5" stopIfTrue="1">
       <formula>"GAP"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="16" operator="equal" dxfId="6" stopIfTrue="1">
+    <cfRule type="cellIs" priority="16" operator="equal" dxfId="5" stopIfTrue="1">
       <formula>"FAIL"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="17" operator="equal" dxfId="6" stopIfTrue="1">
+    <cfRule type="cellIs" priority="17" operator="equal" dxfId="5" stopIfTrue="1">
       <formula>"FAILED"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="18" operator="equal" dxfId="6" stopIfTrue="1">
+    <cfRule type="cellIs" priority="18" operator="equal" dxfId="5" stopIfTrue="1">
       <formula>"BLOCKED"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="19" operator="equal" dxfId="4" stopIfTrue="1">
+    <cfRule type="cellIs" priority="19" operator="equal" dxfId="6" stopIfTrue="1">
       <formula>"OUT"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="20" operator="equal" dxfId="4" stopIfTrue="1">
+    <cfRule type="cellIs" priority="20" operator="equal" dxfId="6" stopIfTrue="1">
       <formula>"PARKED"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="21" operator="equal" dxfId="4" stopIfTrue="1">
+    <cfRule type="cellIs" priority="21" operator="equal" dxfId="6" stopIfTrue="1">
+      <formula>"ON HOLD"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="22" operator="equal" dxfId="6" stopIfTrue="1">
       <formula>"N/A"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A5:F521">
-    <cfRule type="expression" priority="22" dxfId="5">
+    <cfRule type="expression" priority="23" dxfId="0">
       <formula>AND(MOD(ROW(),2)=0,$A5&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8987,64 +7730,52 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="44" customWidth="1" min="2" max="2"/>
-    <col width="70" customWidth="1" min="3" max="3"/>
+    <col width="90" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="24" t="inlineStr">
-        <is>
-          <t>S3 changes</t>
+      <c r="A1" s="19" t="inlineStr">
+        <is>
+          <t>S3 documents</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="27" t="inlineStr">
-        <is>
-          <t>Build item: documents and files in Amazon S3</t>
+      <c r="A2" s="22" t="inlineStr">
+        <is>
+          <t>Documents and files in Amazon S3</t>
         </is>
       </c>
     </row>
     <row r="3" ht="6" customHeight="1">
-      <c r="A3" s="28" t="n"/>
-      <c r="B3" s="28" t="n"/>
-      <c r="C3" s="28" t="n"/>
+      <c r="A3" s="23" t="n"/>
+      <c r="B3" s="23" t="n"/>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="29" t="inlineStr">
+      <c r="A4" s="24" t="inlineStr">
         <is>
           <t>Area</t>
         </is>
       </c>
-      <c r="B4" s="29" t="inlineStr">
-        <is>
-          <t>Today</t>
-        </is>
-      </c>
-      <c r="C4" s="29" t="inlineStr">
-        <is>
-          <t>Change</t>
+      <c r="B4" s="24" t="inlineStr">
+        <is>
+          <t>Proposal</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="12" t="inlineStr">
         <is>
-          <t>Storage port and metadata (ST0)</t>
+          <t>Files and their metadata</t>
         </is>
       </c>
       <c r="B5" s="12" t="inlineStr">
         <is>
-          <t>Each module holds file bytes in its own bytea column</t>
-        </is>
-      </c>
-      <c r="C5" s="12" t="inlineStr">
-        <is>
-          <t>FileStore port in common/storage (S3FileStore, LocalFileStore, MinIO test); shared table stored_file (owner, document type, name, size, SHA-256, bucket, key, version id, retention class, legal hold); module tables get stored_file_id</t>
+          <t>Every file of every module is stored in Amazon S3; PostgreSQL keeps the metadata of each file (owner, document type, name, size, checksum, bucket, key, version, retention class, legal hold)</t>
         </is>
       </c>
     </row>
@@ -9056,12 +7787,7 @@
       </c>
       <c r="B6" s="12" t="inlineStr">
         <is>
-          <t>doc_attachment_content.content bytea (V21, AttachmentService)</t>
-        </is>
-      </c>
-      <c r="C6" s="12" t="inlineStr">
-        <is>
-          <t>Bytes in bibs-&lt;env&gt;-documents; the attachment record points to stored_file (ST1)</t>
+          <t>Stored in the documents bucket of the environment</t>
         </is>
       </c>
     </row>
@@ -9073,12 +7799,7 @@
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
-          <t>plc_slip_file, iss_insurance_advice, bkg_service_invoice, rem_batch_document, clx_billing_document, csh_print_batch, dsb_eod_output (bytea)</t>
-        </is>
-      </c>
-      <c r="C7" s="12" t="inlineStr">
-        <is>
-          <t>Written through FileStore to the documents bucket (ST1); doc_rendition keeps its spec and SHA-256</t>
+          <t>Placement slips, insurance advices, service invoices, remittance and billing documents, print batches and end-of-day outputs are written to the documents bucket; each rendition keeps its specification and checksum</t>
         </is>
       </c>
     </row>
@@ -9090,12 +7811,7 @@
       </c>
       <c r="B8" s="12" t="inlineStr">
         <is>
-          <t>report_run_file, report_batch (bytea); ReportArchiveService</t>
-        </is>
-      </c>
-      <c r="C8" s="12" t="inlineStr">
-        <is>
-          <t>bibs-&lt;env&gt;-reports, expiry per report archive setting (default 400 days); users get a link</t>
+          <t>Stored in the reports bucket, with the expiry of the report archive setting (default 400 days); users get a link</t>
         </is>
       </c>
     </row>
@@ -9107,12 +7823,7 @@
       </c>
       <c r="B9" s="12" t="inlineStr">
         <is>
-          <t>ops_extract_file (FileDropPort), msg_outbound_attachment</t>
-        </is>
-      </c>
-      <c r="C9" s="12" t="inlineStr">
-        <is>
-          <t>FileDropPort writes to S3; e-mail attachments and ZIP bundles are read from S3 and streamed (option B path)</t>
+          <t>Extracts are written to S3; e-mail attachments and ZIP bundles are read from S3</t>
         </is>
       </c>
     </row>
@@ -9124,29 +7835,19 @@
       </c>
       <c r="B10" s="12" t="inlineStr">
         <is>
-          <t>bulk_job keeps only the file name; iss_upload_item bytea; watchlist files as attachments</t>
-        </is>
-      </c>
-      <c r="C10" s="12" t="inlineStr">
-        <is>
-          <t>bibs-&lt;env&gt;-inbound: quarantine prefix until the malware scan tags the object clean; kept 90 days; large files by presigned PUT</t>
+          <t>Inbound bucket with a quarantine area until the malware scan marks the file clean; kept 90 days; large files uploaded directly with a signed link</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t>Migration files (designed)</t>
+          <t>Migration files</t>
         </is>
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
-          <t>mig_extract files; staging purge within 5 days</t>
-        </is>
-      </c>
-      <c r="C11" s="12" t="inlineStr">
-        <is>
-          <t>bibs-&lt;env&gt;-migration, expiry after 5 days, migration role only</t>
+          <t>Migration bucket, expiry after 5 days, migration role only</t>
         </is>
       </c>
     </row>
@@ -9158,12 +7859,7 @@
       </c>
       <c r="B12" s="12" t="inlineStr">
         <is>
-          <t>Backend streams the bytes after the permission check</t>
-        </is>
-      </c>
-      <c r="C12" s="12" t="inlineStr">
-        <is>
-          <t>Presigned GET valid 5 minutes (FILE_LINK_TTL_SECONDS), issued after the permission check, each issue audited; Content-Disposition attachment, no-store</t>
+          <t>A signed link valid 5 minutes (FILE_LINK_TTL_SECONDS), issued after the BIBS permission check, each issue audited; files are downloaded, not cached</t>
         </is>
       </c>
     </row>
@@ -9175,12 +7871,7 @@
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>Database encryption at rest</t>
-        </is>
-      </c>
-      <c r="C13" s="12" t="inlineStr">
-        <is>
-          <t>SSE-KMS with a customer-managed key per environment; deny non-TLS and unencrypted puts; IRSA role and S3 gateway endpoint; keys without personal data</t>
+          <t>SSE-KMS with a customer-managed key per environment; non-TLS and unencrypted uploads refused; access through the application role and an S3 gateway; keys without personal data</t>
         </is>
       </c>
     </row>
@@ -9192,11 +7883,6 @@
       </c>
       <c r="B14" s="12" t="inlineStr">
         <is>
-          <t>Files follow the database backup</t>
-        </is>
-      </c>
-      <c r="C14" s="12" t="inlineStr">
-        <is>
           <t>Versioning; lifecycle Standard, Standard-IA after 90 days, Glacier Instant Retrieval after 1 year; Object Lock governance mode with legal hold; cross-region replication with replication time control</t>
         </is>
       </c>
@@ -9209,12 +7895,7 @@
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C15" s="12" t="inlineStr">
-        <is>
-          <t>One-off copy job per table with SHA-256 check, switch reads, drop the bytea column later (ST1)</t>
+          <t>One-time copy of the existing files with a checksum check before go-live</t>
         </is>
       </c>
     </row>
@@ -9226,12 +7907,7 @@
       </c>
       <c r="B16" s="12" t="inlineStr">
         <is>
-          <t>IER has "Amazon S3 (document store)" with no size</t>
-        </is>
-      </c>
-      <c r="C16" s="12" t="inlineStr">
-        <is>
-          <t>Four buckets per environment; storage estimate per year (to size from the document volumes); KMS keys per environment; S3 gateway endpoint; replication to the DR region; GuardDuty Malware Protection for S3 (or the BDO scanner); Object Lock enabled at bucket creation</t>
+          <t>Four buckets per environment; storage estimate per year (to size from the document volumes); KMS keys per environment; S3 gateway; replication to the DR region; malware scanning of uploads (GuardDuty Malware Protection for S3 or the BDO scanner); Object Lock enabled at bucket creation</t>
         </is>
       </c>
     </row>
@@ -9243,12 +7919,7 @@
       </c>
       <c r="B17" s="12" t="inlineStr">
         <is>
-          <t>Amazon EFS (shared K8s PV); efs-csi-controller pods; "Total PV (GB) EFS" column</t>
-        </is>
-      </c>
-      <c r="C17" s="12" t="inlineStr">
-        <is>
-          <t>Not used by BIBS for documents; pods are stateless</t>
+          <t>Amazon EFS (shared K8s PV), the efs-csi-controller pods and the "Total PV (GB) EFS" column: not used by BIBS for documents; pods are stateless</t>
         </is>
       </c>
     </row>
@@ -9260,22 +7931,17 @@
       </c>
       <c r="B18" s="12" t="inlineStr">
         <is>
-          <t>PROD RDS 2,000 GB, sized with documents in mind</t>
-        </is>
-      </c>
-      <c r="C18" s="12" t="inlineStr">
-        <is>
-          <t>Re-size RDS without file content once the volumes are known; backups and cross-region replica get smaller</t>
+          <t>PROD RDS 2,000 GB was sized with documents in mind; re-size RDS without file content once the volumes are known; backups and the cross-region replica get smaller</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:C18"/>
+  <autoFilter ref="A4:B18"/>
   <mergeCells count="1">
-    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A2:B2"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:C518">
-    <cfRule type="expression" priority="1" dxfId="5">
+  <conditionalFormatting sqref="A5:B518">
+    <cfRule type="expression" priority="1" dxfId="0">
       <formula>AND(MOD(ROW(),2)=0,$A5&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9312,60 +7978,60 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="24" t="inlineStr">
+      <c r="A1" s="19" t="inlineStr">
         <is>
           <t>K8s sizing</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="27" t="inlineStr">
+      <c r="A2" s="22" t="inlineStr">
         <is>
           <t>Replaces the bv-* rows of the IER K8s sheets (to be proved by the performance test)</t>
         </is>
       </c>
     </row>
     <row r="3" ht="6" customHeight="1">
-      <c r="A3" s="28" t="n"/>
-      <c r="B3" s="28" t="n"/>
-      <c r="C3" s="28" t="n"/>
-      <c r="D3" s="28" t="n"/>
-      <c r="E3" s="28" t="n"/>
-      <c r="F3" s="28" t="n"/>
-      <c r="G3" s="28" t="n"/>
+      <c r="A3" s="23" t="n"/>
+      <c r="B3" s="23" t="n"/>
+      <c r="C3" s="23" t="n"/>
+      <c r="D3" s="23" t="n"/>
+      <c r="E3" s="23" t="n"/>
+      <c r="F3" s="23" t="n"/>
+      <c r="G3" s="23" t="n"/>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="29" t="inlineStr">
+      <c r="A4" s="24" t="inlineStr">
         <is>
           <t>Environment</t>
         </is>
       </c>
-      <c r="B4" s="29" t="inlineStr">
+      <c r="B4" s="24" t="inlineStr">
         <is>
           <t>Deployment</t>
         </is>
       </c>
-      <c r="C4" s="29" t="inlineStr">
+      <c r="C4" s="24" t="inlineStr">
         <is>
           <t>Min replicas</t>
         </is>
       </c>
-      <c r="D4" s="29" t="inlineStr">
+      <c r="D4" s="24" t="inlineStr">
         <is>
           <t>Max replicas</t>
         </is>
       </c>
-      <c r="E4" s="29" t="inlineStr">
+      <c r="E4" s="24" t="inlineStr">
         <is>
           <t>Requests CPU / memory</t>
         </is>
       </c>
-      <c r="F4" s="29" t="inlineStr">
+      <c r="F4" s="24" t="inlineStr">
         <is>
           <t>Limits CPU / memory</t>
         </is>
       </c>
-      <c r="G4" s="29" t="inlineStr">
+      <c r="G4" s="24" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
@@ -9700,7 +8366,7 @@
       </c>
       <c r="G13" s="12" t="inlineStr">
         <is>
-          <t>HPA on CPU; PodDisruptionBudget minAvailable 2; spread over 3 AZs</t>
+          <t>HPA on CPU; pod disruption budget minAvailable 2; spread over 3 AZs</t>
         </is>
       </c>
     </row>
@@ -9821,7 +8487,7 @@
     <mergeCell ref="A2:G2"/>
   </mergeCells>
   <conditionalFormatting sqref="A5:G516">
-    <cfRule type="expression" priority="1" dxfId="5">
+    <cfRule type="expression" priority="1" dxfId="0">
       <formula>AND(MOD(ROW(),2)=0,$A5&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>

--- a/docs/deliverables/out/Programme/Alignment/BIBS_Alignment_BRD-00_Integration_Inventory_v1.0.xlsx
+++ b/docs/deliverables/out/Programme/Alignment/BIBS_Alignment_BRD-00_Integration_Inventory_v1.0.xlsx
@@ -7229,17 +7229,17 @@
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>Redis 7 with cluster mode disabled (one shard, primary + replica, TLS, AUTH); the cache clear uses SCAN and the job lock uses scripts on single keys</t>
+          <t>Valkey 8 (BSD-3-Clause, same protocol as Redis; Amazon ElastiCache for Valkey) with cluster mode disabled (one shard, primary + replica, TLS, AUTH); the cache clear uses SCAN and the job lock uses scripts on single keys</t>
         </is>
       </c>
       <c r="D9" s="25" t="inlineStr">
         <is>
-          <t>Mismatch (wording)</t>
+          <t>Mismatch (engine, wording)</t>
         </is>
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>IER: cluster mode disabled, Multi-AZ replica. A change in BIBS only if cluster mode enabled is imposed</t>
+          <t>IER: ElastiCache for Valkey 8 in place of Redis 7.x (client decision of 08-Oct-2026: Redis 7.4 and later are no longer under the BSD licence); cluster mode disabled, Multi-AZ replica. A change in BIBS only if cluster mode enabled is imposed</t>
         </is>
       </c>
       <c r="F9" s="12" t="inlineStr">
@@ -7261,17 +7261,17 @@
       </c>
       <c r="C10" s="12" t="inlineStr">
         <is>
-          <t>MSK Kafka 3.6+ with SASL/SCRAM + TLS, 9 topics plus dead-letter topics, transactional outbox; no EventBridge, no schema registry</t>
+          <t>MSK Kafka 3.9 (KRaft) with SASL/SCRAM + TLS, 9 topics plus dead-letter topics, transactional outbox; no EventBridge, no schema registry</t>
         </is>
       </c>
       <c r="D10" s="25" t="inlineStr">
         <is>
-          <t>Aligned (MSK); Mismatch (EventBridge, 80 topics)</t>
+          <t>Aligned (MSK); Mismatch (version, EventBridge, 80 topics)</t>
         </is>
       </c>
       <c r="E10" s="12" t="inlineStr">
         <is>
-          <t>IER: 3 brokers kafka.m5.large class, 9 topics x 3 partitions; DEV / SIT with 2 brokers need a replication factor of 2</t>
+          <t>IER: Kafka 3.9 (KRaft), 3 brokers kafka.m5.large class, 9 topics x 3 partitions; DEV / SIT with 2 brokers need a replication factor of 2</t>
         </is>
       </c>
       <c r="F10" s="12" t="inlineStr">
@@ -7325,17 +7325,17 @@
       </c>
       <c r="C12" s="12" t="inlineStr">
         <is>
-          <t>Kubernetes Ingress to the nginx frontend, API calls proxied to the backend; JWT issued by BIBS; login rate limit in the application</t>
+          <t>Kubernetes Gateway API: Route 53 + AWS WAF + internal ALB (AWS Load Balancer Controller) for users, Apigee X for the system APIs; HTTPS to the pods; JWT issued by BIBS; login rate limit in the application</t>
         </is>
       </c>
       <c r="D12" s="25" t="inlineStr">
         <is>
-          <t>Gap</t>
+          <t>Mismatch</t>
         </is>
       </c>
       <c r="E12" s="12" t="inlineStr">
         <is>
-          <t>Agree one edge: Route 53 + WAF + ALB (AWS Load Balancer Controller) or ingress-nginx; Apigee only if BDO mandates it for internal APIs</t>
+          <t>IER: a Gateway API controller in place of ingress-nginx (retired by the Kubernetes project in March 2026): the AWS Load Balancer Controller, or Envoy Gateway where an environment needs it; no CloudFront, no Istio</t>
         </is>
       </c>
       <c r="F12" s="12" t="inlineStr">
@@ -8144,7 +8144,7 @@
       </c>
       <c r="G7" s="12" t="inlineStr">
         <is>
-          <t>Two pods to test the Redis job lock and cache eviction across pods</t>
+          <t>Two pods to test the Valkey job lock and cache eviction across pods</t>
         </is>
       </c>
     </row>
